--- a/Backtest_Lay_2x2_Agosto_2026.xlsx
+++ b/Backtest_Lay_2x2_Agosto_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,38 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +64,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,13 +464,4594 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
+    <col width="61" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Horário</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Liga</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Confronto</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Método</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Lado</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 Betfair</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Gols Mandante</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Gols Visitante</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado (GREEN/RED)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro/Prejuízo (Stake R$100)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro/Prejuízo (Liab R$200)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Justificativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Jeonbuk x Seoul</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 2</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Asan x Seongnam</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CHINA 2</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ningbo Professional x Guangxi Hengchen</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Tianjin Jinmen Tiger x Yunnan Yukun</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Beijing Guoan x Zhejiang Professional</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shanghai Port x Shandong Taishan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>SWEDEN 2</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Varberg x Falkenberg</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ICELAND 1</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Vestmannaeyjar x Fram</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Fredrikstad x Sandefjord</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 2</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Bryne x Stromsgodset</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>SWEDEN 2</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Brage x Landskrona</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>SWEDEN 2</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Norrkoping x Helsingborg</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>FINLAND 1</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Gnistan x KuPS</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Start x Viking</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>FC Cajamarca x Sport Huancayo</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Real Oruro x Independiente</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>CHILE 1</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Everton x Colo Colo</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>SA Bulo Bulo x Blooming</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>CF Montreal x New England Revolution</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>-1550</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>DC United x Nashville SC</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>-1600</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Inter Miami x Columbus Crew</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>-1450</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>New York Red Bulls x Orlando City</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Philadelphia Union x Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps x Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Chicago Fire x Charlotte</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Minnesota United x San Diego FC</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City x Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>St. Louis City x Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Junior x Millonarios</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Colorado Rapids x Austin FC</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>FC Cincinnati x San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy x FC Dallas</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Portland Timbers x Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Qingdao West Coast x Qingdao Hainiu</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 1</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Ulsan HD x Anyang</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 2</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Busan x Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Shenzhen Xinpengcheng x Chongqing Tonglianglong</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>SWEDEN 1</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna x Malmo FF</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>SWEDEN 1</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Goteborg x Degerfors</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>ESTONIA 1</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Kalju x Tammeka</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>FINLAND 1</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>AC Oulu x Ilves</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>ICELAND 1</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Akranes x Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>-1550</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>IRELAND 1</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Waterford x Shelbourne</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>KFUM Oslo x Kristiansund</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Molde x Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 2</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Hodd x Moss</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 2</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Lyn x Sogndal</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 2</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Raufoss x Stabaek</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>CHILE 1</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>D. Concepcion x U. Catolica</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Brann x Rosenborg</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>CHILE 1</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>La Serena x O'Higgins</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Always Ready x Bolivar</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero x Nacional Potosi</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>FINLAND 1</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>SJK x HJK</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>IRELAND 2</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Kerry x Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>IRELAND 2</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>UC Dublin x Treaty United</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>IRELAND 2</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Wexford x Bray</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 2</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Ranheim x Haugesund</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>SWEDEN 2</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Orebro x Varnamo</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>ICELAND 1</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Valur x Stjarnan</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Academia del Balompie x Real Oruro</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Independiente x Aurora</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>VENEZUELA 1</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Universidad Central x Monagas</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>BRAZIL CUP</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Remo x Santos</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>ICELAND 1</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Keflavik x KA Akureyri</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>ICELAND 1</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur x KR Reykjavik</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Nacional Potosi x The Strongest</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>USA 2</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>El Paso x Monterey Bay</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto x Real Potosi</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>ICELAND 2</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>IR Reykjavik x Aegir</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>VENEZUELA 1</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Rayo Zuliano x Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>BOLIVIA 1</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Blooming x Always Ready</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 2</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Hwaseong x Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>ESTONIA 1</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Kuressaare x Harju JK Laagri</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>FINLAND 1</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>SJK x Gnistan</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-1350</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Sandefjord x KFUM Oslo</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>IRELAND 2</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Athlone x Longford</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>IRELAND 2</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>UC Dublin x Wexford</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>IRELAND 1</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Galway x Drogheda</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Quant</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Backtest_Lay_2x2_Agosto_2026.xlsx
+++ b/Backtest_Lay_2x2_Agosto_2026.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M451"/>
+  <dimension ref="A1:O451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,8 @@
     <col width="32" customWidth="1" min="11" max="11"/>
     <col width="31" customWidth="1" min="12" max="12"/>
     <col width="61" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,6 +558,16 @@
           <t>Justificativa</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro/Prejuízo (Stake R)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro/Prejuízo (Liab R)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -613,6 +625,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N2" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -670,6 +688,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N3" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -727,6 +751,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N4" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -784,6 +814,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N5" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -841,6 +877,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N6" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -898,6 +940,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N7" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -955,6 +1003,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N8" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1012,6 +1066,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N9" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1069,6 +1129,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N10" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1126,6 +1192,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N11" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1183,6 +1255,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N12" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1240,6 +1318,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N13" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1297,6 +1381,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N14" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1354,6 +1444,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N15" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1411,6 +1507,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N16" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1468,6 +1570,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N17" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1525,6 +1633,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N18" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1582,6 +1696,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N19" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1639,6 +1759,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N20" s="3" t="n">
+        <v>-1550</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1696,6 +1822,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N21" s="3" t="n">
+        <v>-1600</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1753,6 +1885,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N22" s="3" t="n">
+        <v>-1450</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1810,6 +1948,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N23" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1867,6 +2011,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N24" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1924,6 +2074,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N25" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1981,6 +2137,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N26" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2038,6 +2200,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N27" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2095,6 +2263,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N28" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2152,6 +2326,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N29" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2209,6 +2389,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N30" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2266,6 +2452,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N31" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2323,6 +2515,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N32" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2380,6 +2578,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N33" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2437,6 +2641,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N34" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2494,6 +2704,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N35" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2551,6 +2767,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N36" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2608,6 +2830,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N37" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2665,6 +2893,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N38" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2722,6 +2956,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N39" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2779,6 +3019,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N40" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2836,6 +3082,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N41" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2893,6 +3145,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N42" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2950,6 +3208,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N43" s="3" t="n">
+        <v>-1550</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3007,6 +3271,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N44" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3064,6 +3334,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N45" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3121,6 +3397,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N46" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3178,6 +3460,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N47" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3235,6 +3523,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N48" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3292,6 +3586,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N49" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3349,6 +3649,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N50" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3406,6 +3712,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N51" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3463,6 +3775,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N52" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3520,6 +3838,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N53" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3577,6 +3901,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N54" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3634,6 +3964,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N55" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3691,6 +4027,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N56" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3748,6 +4090,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N57" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3805,6 +4153,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N58" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3862,6 +4216,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N59" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3919,6 +4279,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N60" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3976,6 +4342,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N61" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4033,6 +4405,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N62" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4090,6 +4468,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N63" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4147,6 +4531,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N64" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4204,6 +4594,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N65" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4261,6 +4657,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N66" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4318,6 +4720,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N67" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4375,6 +4783,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N68" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4432,6 +4846,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N69" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4489,6 +4909,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N70" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4546,6 +4972,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N71" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4603,6 +5035,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N72" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4660,6 +5098,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N73" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4717,6 +5161,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N74" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4774,6 +5224,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N75" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4831,6 +5287,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N76" s="3" t="n">
+        <v>-1350</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4888,6 +5350,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N77" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4945,6 +5413,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N78" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5002,6 +5476,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N79" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5059,6 +5539,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N80" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5116,6 +5602,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N81" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5173,6 +5665,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N82" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5230,6 +5728,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N83" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5287,6 +5791,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N84" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5344,6 +5854,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N85" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5401,6 +5917,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N86" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5458,6 +5980,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N87" s="3" t="n">
+        <v>-1450</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5515,6 +6043,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N88" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5572,6 +6106,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N89" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5629,6 +6169,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N90" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5686,6 +6232,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N91" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5743,6 +6295,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N92" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5800,6 +6358,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N93" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5857,6 +6421,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N94" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5914,6 +6484,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N95" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5971,6 +6547,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N96" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6028,6 +6610,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N97" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6085,6 +6673,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N98" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6142,6 +6736,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N99" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6199,6 +6799,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N100" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6256,6 +6862,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N101" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6313,6 +6925,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N102" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6370,6 +6988,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N103" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O103" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6427,6 +7051,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N104" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O104" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6484,6 +7114,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N105" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6541,6 +7177,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N106" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O106" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6598,6 +7240,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N107" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O107" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6655,6 +7303,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N108" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O108" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6712,6 +7366,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N109" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O109" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6769,6 +7429,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N110" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O110" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6826,6 +7492,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N111" s="3" t="n">
+        <v>-1550</v>
+      </c>
+      <c r="O111" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6883,6 +7555,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N112" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O112" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6940,6 +7618,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N113" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O113" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6997,6 +7681,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N114" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O114" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7054,6 +7744,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N115" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O115" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7111,6 +7807,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N116" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O116" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7168,6 +7870,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N117" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O117" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7225,6 +7933,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N118" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O118" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7282,6 +7996,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N119" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O119" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7339,6 +8059,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N120" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O120" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7396,6 +8122,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N121" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O121" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7453,6 +8185,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N122" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O122" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7510,6 +8248,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N123" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O123" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7567,6 +8311,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N124" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O124" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7624,6 +8374,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N125" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O125" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7681,6 +8437,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N126" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O126" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7738,6 +8500,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N127" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O127" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7795,6 +8563,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N128" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7852,6 +8626,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N129" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7909,6 +8689,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N130" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7966,6 +8752,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N131" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O131" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8023,6 +8815,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N132" s="3" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="O132" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8080,6 +8878,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N133" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8137,6 +8941,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N134" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8194,6 +9004,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N135" s="3" t="n">
+        <v>-1600</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8251,6 +9067,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N136" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O136" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8308,6 +9130,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N137" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O137" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8365,6 +9193,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N138" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O138" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8422,6 +9256,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N139" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O139" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8479,6 +9319,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N140" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O140" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8536,6 +9382,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N141" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O141" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8593,6 +9445,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N142" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O142" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8650,6 +9508,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N143" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O143" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8707,6 +9571,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N144" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O144" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8764,6 +9634,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N145" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O145" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8821,6 +9697,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N146" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O146" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8878,6 +9760,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N147" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O147" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -8935,6 +9823,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N148" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O148" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -8992,6 +9886,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N149" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O149" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9049,6 +9949,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N150" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O150" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9106,6 +10012,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N151" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O151" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9163,6 +10075,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N152" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O152" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9220,6 +10138,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N153" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O153" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -9277,6 +10201,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N154" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O154" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -9334,6 +10264,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N155" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O155" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9391,6 +10327,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N156" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O156" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -9448,6 +10390,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N157" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O157" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -9505,6 +10453,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N158" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O158" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -9562,6 +10516,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N159" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O159" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9619,6 +10579,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N160" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O160" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9676,6 +10642,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N161" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O161" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9733,6 +10705,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N162" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O162" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9790,6 +10768,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N163" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O163" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9847,6 +10831,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N164" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O164" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9904,6 +10894,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N165" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O165" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9961,6 +10957,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N166" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O166" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -10018,6 +11020,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N167" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O167" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -10075,6 +11083,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N168" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O168" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10132,6 +11146,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N169" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O169" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -10189,6 +11209,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N170" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O170" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -10246,6 +11272,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N171" s="3" t="n">
+        <v>-1350</v>
+      </c>
+      <c r="O171" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -10303,6 +11335,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N172" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O172" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10360,6 +11398,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N173" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O173" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10395,15 +11439,31 @@
       <c r="G174" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H174" s="6" t="inlineStr"/>
-      <c r="I174" s="6" t="inlineStr"/>
-      <c r="J174" s="6" t="inlineStr"/>
-      <c r="K174" s="6" t="inlineStr"/>
-      <c r="L174" s="6" t="inlineStr"/>
+      <c r="H174" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I174" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J174" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K174" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L174" s="6" t="n">
+        <v/>
+      </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N174" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O174" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -10462,6 +11522,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N175" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O175" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10519,6 +11585,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N176" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O176" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -10576,6 +11648,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N177" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O177" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10633,6 +11711,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N178" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O178" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -10690,6 +11774,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N179" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O179" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -10747,6 +11837,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N180" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O180" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -10804,6 +11900,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N181" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O181" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10839,15 +11941,31 @@
       <c r="G182" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H182" s="6" t="inlineStr"/>
-      <c r="I182" s="6" t="inlineStr"/>
-      <c r="J182" s="6" t="inlineStr"/>
-      <c r="K182" s="6" t="inlineStr"/>
-      <c r="L182" s="6" t="inlineStr"/>
+      <c r="H182" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J182" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K182" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L182" s="6" t="n">
+        <v/>
+      </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N182" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O182" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="183">
@@ -10906,6 +12024,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N183" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O183" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10963,6 +12087,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N184" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O184" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -11020,6 +12150,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N185" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O185" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -11077,6 +12213,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N186" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O186" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -11134,6 +12276,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N187" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O187" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -11191,6 +12339,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N188" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O188" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -11248,6 +12402,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N189" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O189" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -11305,6 +12465,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N190" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O190" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -11362,6 +12528,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N191" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O191" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -11419,6 +12591,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N192" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O192" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -11476,6 +12654,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N193" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O193" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -11511,15 +12695,31 @@
       <c r="G194" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H194" s="6" t="inlineStr"/>
-      <c r="I194" s="6" t="inlineStr"/>
-      <c r="J194" s="6" t="inlineStr"/>
-      <c r="K194" s="6" t="inlineStr"/>
-      <c r="L194" s="6" t="inlineStr"/>
+      <c r="H194" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I194" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J194" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K194" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L194" s="6" t="n">
+        <v/>
+      </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N194" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O194" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="195">
@@ -11578,6 +12778,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N195" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O195" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -11635,6 +12841,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N196" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O196" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -11692,6 +12904,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N197" s="3" t="n">
+        <v>-1700</v>
+      </c>
+      <c r="O197" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -11749,6 +12967,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N198" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O198" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -11806,6 +13030,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N199" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O199" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -11841,15 +13071,31 @@
       <c r="G200" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H200" s="6" t="inlineStr"/>
-      <c r="I200" s="6" t="inlineStr"/>
-      <c r="J200" s="6" t="inlineStr"/>
-      <c r="K200" s="6" t="inlineStr"/>
-      <c r="L200" s="6" t="inlineStr"/>
+      <c r="H200" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I200" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J200" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K200" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L200" s="6" t="n">
+        <v/>
+      </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N200" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O200" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="201">
@@ -11886,15 +13132,33 @@
       <c r="G201" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="H201" s="6" t="inlineStr"/>
-      <c r="I201" s="6" t="inlineStr"/>
-      <c r="J201" s="6" t="inlineStr"/>
-      <c r="K201" s="6" t="inlineStr"/>
-      <c r="L201" s="6" t="inlineStr"/>
+      <c r="H201" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K201" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L201" s="4" t="n">
+        <v/>
+      </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N201" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O201" s="3" t="n">
+        <v>15.2</v>
       </c>
     </row>
     <row r="202">
@@ -11931,15 +13195,31 @@
       <c r="G202" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H202" s="6" t="inlineStr"/>
-      <c r="I202" s="6" t="inlineStr"/>
-      <c r="J202" s="6" t="inlineStr"/>
-      <c r="K202" s="6" t="inlineStr"/>
-      <c r="L202" s="6" t="inlineStr"/>
+      <c r="H202" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I202" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J202" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K202" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L202" s="6" t="n">
+        <v/>
+      </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N202" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O202" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="203">
@@ -11998,6 +13278,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N203" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O203" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -12055,6 +13341,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N204" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O204" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -12112,6 +13404,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N205" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O205" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -12169,6 +13467,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N206" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O206" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -12226,6 +13530,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N207" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O207" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -12283,6 +13593,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N208" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O208" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -12340,6 +13656,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N209" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O209" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -12397,6 +13719,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N210" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O210" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -12454,6 +13782,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N211" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O211" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -12511,6 +13845,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N212" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O212" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -12568,6 +13908,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N213" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O213" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -12625,6 +13971,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N214" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O214" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -12682,6 +14034,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N215" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O215" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -12739,6 +14097,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N216" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O216" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -12796,6 +14160,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N217" s="3" t="n">
+        <v>-1550</v>
+      </c>
+      <c r="O217" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -12853,6 +14223,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N218" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O218" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -12910,6 +14286,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N219" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O219" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -12967,6 +14349,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N220" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O220" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -13024,6 +14412,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N221" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O221" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -13081,6 +14475,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N222" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O222" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -13138,6 +14538,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N223" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O223" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -13195,6 +14601,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N224" s="3" t="n">
+        <v>-1700</v>
+      </c>
+      <c r="O224" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -13252,6 +14664,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N225" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O225" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -13309,6 +14727,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N226" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O226" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -13366,6 +14790,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N227" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O227" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -13423,6 +14853,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N228" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O228" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -13480,6 +14916,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N229" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O229" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -13537,6 +14979,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N230" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O230" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -13594,6 +15042,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N231" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O231" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -13651,6 +15105,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N232" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O232" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -13708,6 +15168,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N233" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O233" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -13765,6 +15231,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N234" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O234" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -13822,6 +15294,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N235" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O235" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -13879,6 +15357,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N236" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O236" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -13936,6 +15420,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N237" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O237" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -13993,6 +15483,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N238" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O238" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -14050,6 +15546,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N239" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O239" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -14107,6 +15609,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N240" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O240" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -14164,6 +15672,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N241" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O241" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -14199,15 +15713,31 @@
       <c r="G242" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H242" s="6" t="inlineStr"/>
-      <c r="I242" s="6" t="inlineStr"/>
-      <c r="J242" s="6" t="inlineStr"/>
-      <c r="K242" s="6" t="inlineStr"/>
-      <c r="L242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I242" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J242" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K242" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L242" s="6" t="n">
+        <v/>
+      </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N242" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O242" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="243">
@@ -14244,15 +15774,33 @@
       <c r="G243" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="H243" s="6" t="inlineStr"/>
-      <c r="I243" s="6" t="inlineStr"/>
-      <c r="J243" s="6" t="inlineStr"/>
-      <c r="K243" s="6" t="inlineStr"/>
-      <c r="L243" s="6" t="inlineStr"/>
+      <c r="H243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K243" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L243" s="4" t="n">
+        <v/>
+      </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N243" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O243" s="3" t="n">
+        <v>14.07</v>
       </c>
     </row>
     <row r="244">
@@ -14289,15 +15837,31 @@
       <c r="G244" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H244" s="6" t="inlineStr"/>
-      <c r="I244" s="6" t="inlineStr"/>
-      <c r="J244" s="6" t="inlineStr"/>
-      <c r="K244" s="6" t="inlineStr"/>
-      <c r="L244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I244" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J244" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K244" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L244" s="6" t="n">
+        <v/>
+      </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N244" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O244" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="245">
@@ -14356,6 +15920,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N245" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O245" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -14413,6 +15983,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N246" s="3" t="n">
+        <v>-1350</v>
+      </c>
+      <c r="O246" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -14448,15 +16024,31 @@
       <c r="G247" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H247" s="6" t="inlineStr"/>
-      <c r="I247" s="6" t="inlineStr"/>
-      <c r="J247" s="6" t="inlineStr"/>
-      <c r="K247" s="6" t="inlineStr"/>
-      <c r="L247" s="6" t="inlineStr"/>
+      <c r="H247" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I247" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J247" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K247" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L247" s="6" t="n">
+        <v/>
+      </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N247" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O247" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="248">
@@ -14493,15 +16085,31 @@
       <c r="G248" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H248" s="6" t="inlineStr"/>
-      <c r="I248" s="6" t="inlineStr"/>
-      <c r="J248" s="6" t="inlineStr"/>
-      <c r="K248" s="6" t="inlineStr"/>
-      <c r="L248" s="6" t="inlineStr"/>
+      <c r="H248" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I248" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J248" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K248" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L248" s="6" t="n">
+        <v/>
+      </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N248" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O248" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="249">
@@ -14560,6 +16168,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N249" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O249" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -14595,15 +16209,31 @@
       <c r="G250" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H250" s="6" t="inlineStr"/>
-      <c r="I250" s="6" t="inlineStr"/>
-      <c r="J250" s="6" t="inlineStr"/>
-      <c r="K250" s="6" t="inlineStr"/>
-      <c r="L250" s="6" t="inlineStr"/>
+      <c r="H250" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I250" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J250" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K250" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L250" s="6" t="n">
+        <v/>
+      </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N250" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O250" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="251">
@@ -14662,6 +16292,12 @@
           <t>Odd Lay 2x2 (13.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N251" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O251" s="3" t="n">
+        <v>15.83</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -14697,15 +16333,33 @@
       <c r="G252" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H252" s="6" t="inlineStr"/>
-      <c r="I252" s="6" t="inlineStr"/>
-      <c r="J252" s="6" t="inlineStr"/>
-      <c r="K252" s="6" t="inlineStr"/>
-      <c r="L252" s="6" t="inlineStr"/>
+      <c r="H252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K252" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L252" s="4" t="n">
+        <v/>
+      </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N252" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O252" s="3" t="n">
+        <v>11.88</v>
       </c>
     </row>
     <row r="253">
@@ -14742,15 +16396,33 @@
       <c r="G253" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="H253" s="6" t="inlineStr"/>
-      <c r="I253" s="6" t="inlineStr"/>
-      <c r="J253" s="6" t="inlineStr"/>
-      <c r="K253" s="6" t="inlineStr"/>
-      <c r="L253" s="6" t="inlineStr"/>
+      <c r="H253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K253" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L253" s="4" t="n">
+        <v/>
+      </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N253" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O253" s="3" t="n">
+        <v>11.52</v>
       </c>
     </row>
     <row r="254">
@@ -14809,6 +16481,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N254" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O254" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -14866,6 +16544,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N255" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O255" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -14923,6 +16607,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N256" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O256" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -14980,6 +16670,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N257" s="3" t="n">
+        <v>-1600</v>
+      </c>
+      <c r="O257" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -15037,6 +16733,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N258" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O258" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -15094,6 +16796,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N259" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O259" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -15151,6 +16859,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N260" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O260" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -15208,6 +16922,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N261" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O261" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -15265,6 +16985,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N262" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O262" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -15322,6 +17048,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N263" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O263" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -15357,15 +17089,33 @@
       <c r="G264" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H264" s="6" t="inlineStr"/>
-      <c r="I264" s="6" t="inlineStr"/>
-      <c r="J264" s="6" t="inlineStr"/>
-      <c r="K264" s="6" t="inlineStr"/>
-      <c r="L264" s="6" t="inlineStr"/>
+      <c r="H264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K264" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L264" s="4" t="n">
+        <v/>
+      </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N264" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O264" s="3" t="n">
+        <v>12.67</v>
       </c>
     </row>
     <row r="265">
@@ -15424,6 +17174,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N265" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O265" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -15481,6 +17237,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N266" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O266" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -15538,6 +17300,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N267" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O267" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -15595,6 +17363,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N268" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O268" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -15652,6 +17426,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N269" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O269" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -15709,6 +17489,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N270" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O270" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -15766,6 +17552,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N271" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O271" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -15823,6 +17615,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N272" s="3" t="n">
+        <v>-1550</v>
+      </c>
+      <c r="O272" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -15880,6 +17678,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N273" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O273" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -15915,15 +17719,33 @@
       <c r="G274" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H274" s="6" t="inlineStr"/>
-      <c r="I274" s="6" t="inlineStr"/>
-      <c r="J274" s="6" t="inlineStr"/>
-      <c r="K274" s="6" t="inlineStr"/>
-      <c r="L274" s="6" t="inlineStr"/>
+      <c r="H274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K274" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L274" s="4" t="n">
+        <v/>
+      </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N274" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O274" s="3" t="n">
+        <v>12.26</v>
       </c>
     </row>
     <row r="275">
@@ -15960,15 +17782,33 @@
       <c r="G275" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H275" s="6" t="inlineStr"/>
-      <c r="I275" s="6" t="inlineStr"/>
-      <c r="J275" s="6" t="inlineStr"/>
-      <c r="K275" s="6" t="inlineStr"/>
-      <c r="L275" s="6" t="inlineStr"/>
+      <c r="H275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K275" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L275" s="4" t="n">
+        <v/>
+      </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N275" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O275" s="3" t="n">
+        <v>11.88</v>
       </c>
     </row>
     <row r="276">
@@ -16005,15 +17845,33 @@
       <c r="G276" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H276" s="6" t="inlineStr"/>
-      <c r="I276" s="6" t="inlineStr"/>
-      <c r="J276" s="6" t="inlineStr"/>
-      <c r="K276" s="6" t="inlineStr"/>
-      <c r="L276" s="6" t="inlineStr"/>
+      <c r="H276" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K276" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L276" s="4" t="n">
+        <v/>
+      </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N276" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O276" s="3" t="n">
+        <v>13.1</v>
       </c>
     </row>
     <row r="277">
@@ -16072,6 +17930,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N277" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O277" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -16107,15 +17971,33 @@
       <c r="G278" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H278" s="6" t="inlineStr"/>
-      <c r="I278" s="6" t="inlineStr"/>
-      <c r="J278" s="6" t="inlineStr"/>
-      <c r="K278" s="6" t="inlineStr"/>
-      <c r="L278" s="6" t="inlineStr"/>
+      <c r="H278" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K278" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L278" s="4" t="n">
+        <v/>
+      </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N278" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O278" s="3" t="n">
+        <v>11.88</v>
       </c>
     </row>
     <row r="279">
@@ -16174,6 +18056,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N279" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O279" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -16209,15 +18097,33 @@
       <c r="G280" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H280" s="6" t="inlineStr"/>
-      <c r="I280" s="6" t="inlineStr"/>
-      <c r="J280" s="6" t="inlineStr"/>
-      <c r="K280" s="6" t="inlineStr"/>
-      <c r="L280" s="6" t="inlineStr"/>
+      <c r="H280" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K280" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L280" s="4" t="n">
+        <v/>
+      </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N280" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O280" s="3" t="n">
+        <v>12.67</v>
       </c>
     </row>
     <row r="281">
@@ -16276,6 +18182,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N281" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O281" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -16333,6 +18245,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N282" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O282" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -16390,6 +18308,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N283" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O283" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -16425,15 +18349,33 @@
       <c r="G284" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H284" s="6" t="inlineStr"/>
-      <c r="I284" s="6" t="inlineStr"/>
-      <c r="J284" s="6" t="inlineStr"/>
-      <c r="K284" s="6" t="inlineStr"/>
-      <c r="L284" s="6" t="inlineStr"/>
+      <c r="H284" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K284" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L284" s="4" t="n">
+        <v/>
+      </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N284" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O284" s="3" t="n">
+        <v>13.57</v>
       </c>
     </row>
     <row r="285">
@@ -16492,6 +18434,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N285" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O285" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -16549,6 +18497,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N286" s="3" t="n">
+        <v>-1650</v>
+      </c>
+      <c r="O286" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -16606,6 +18560,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N287" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O287" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -16663,6 +18623,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N288" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O288" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -16720,6 +18686,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N289" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O289" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -16777,6 +18749,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N290" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O290" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -16834,6 +18812,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N291" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O291" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -16891,6 +18875,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N292" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O292" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -16926,15 +18916,31 @@
       <c r="G293" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H293" s="6" t="inlineStr"/>
-      <c r="I293" s="6" t="inlineStr"/>
-      <c r="J293" s="6" t="inlineStr"/>
-      <c r="K293" s="6" t="inlineStr"/>
-      <c r="L293" s="6" t="inlineStr"/>
+      <c r="H293" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I293" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J293" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K293" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L293" s="6" t="n">
+        <v/>
+      </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N293" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O293" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="294">
@@ -16971,15 +18977,33 @@
       <c r="G294" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H294" s="6" t="inlineStr"/>
-      <c r="I294" s="6" t="inlineStr"/>
-      <c r="J294" s="6" t="inlineStr"/>
-      <c r="K294" s="6" t="inlineStr"/>
-      <c r="L294" s="6" t="inlineStr"/>
+      <c r="H294" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I294" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K294" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L294" s="4" t="n">
+        <v/>
+      </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N294" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O294" s="3" t="n">
+        <v>13.1</v>
       </c>
     </row>
     <row r="295">
@@ -17016,15 +19040,33 @@
       <c r="G295" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H295" s="6" t="inlineStr"/>
-      <c r="I295" s="6" t="inlineStr"/>
-      <c r="J295" s="6" t="inlineStr"/>
-      <c r="K295" s="6" t="inlineStr"/>
-      <c r="L295" s="6" t="inlineStr"/>
+      <c r="H295" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I295" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J295" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K295" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L295" s="4" t="n">
+        <v/>
+      </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N295" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O295" s="3" t="n">
+        <v>12.67</v>
       </c>
     </row>
     <row r="296">
@@ -17061,15 +19103,31 @@
       <c r="G296" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H296" s="6" t="inlineStr"/>
-      <c r="I296" s="6" t="inlineStr"/>
-      <c r="J296" s="6" t="inlineStr"/>
-      <c r="K296" s="6" t="inlineStr"/>
-      <c r="L296" s="6" t="inlineStr"/>
+      <c r="H296" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I296" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J296" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K296" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L296" s="6" t="n">
+        <v/>
+      </c>
       <c r="M296" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N296" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O296" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="297">
@@ -17106,15 +19164,33 @@
       <c r="G297" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H297" s="6" t="inlineStr"/>
-      <c r="I297" s="6" t="inlineStr"/>
-      <c r="J297" s="6" t="inlineStr"/>
-      <c r="K297" s="6" t="inlineStr"/>
-      <c r="L297" s="6" t="inlineStr"/>
+      <c r="H297" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K297" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L297" s="4" t="n">
+        <v/>
+      </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N297" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O297" s="3" t="n">
+        <v>11.18</v>
       </c>
     </row>
     <row r="298">
@@ -17173,6 +19249,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N298" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O298" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -17208,15 +19290,33 @@
       <c r="G299" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H299" s="6" t="inlineStr"/>
-      <c r="I299" s="6" t="inlineStr"/>
-      <c r="J299" s="6" t="inlineStr"/>
-      <c r="K299" s="6" t="inlineStr"/>
-      <c r="L299" s="6" t="inlineStr"/>
+      <c r="H299" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K299" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L299" s="4" t="n">
+        <v/>
+      </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N299" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O299" s="3" t="n">
+        <v>13.1</v>
       </c>
     </row>
     <row r="300">
@@ -17253,15 +19353,33 @@
       <c r="G300" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H300" s="6" t="inlineStr"/>
-      <c r="I300" s="6" t="inlineStr"/>
-      <c r="J300" s="6" t="inlineStr"/>
-      <c r="K300" s="6" t="inlineStr"/>
-      <c r="L300" s="6" t="inlineStr"/>
+      <c r="H300" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K300" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L300" s="4" t="n">
+        <v/>
+      </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N300" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O300" s="3" t="n">
+        <v>12.67</v>
       </c>
     </row>
     <row r="301">
@@ -17298,15 +19416,31 @@
       <c r="G301" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H301" s="6" t="inlineStr"/>
-      <c r="I301" s="6" t="inlineStr"/>
-      <c r="J301" s="6" t="inlineStr"/>
-      <c r="K301" s="6" t="inlineStr"/>
-      <c r="L301" s="6" t="inlineStr"/>
+      <c r="H301" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I301" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J301" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K301" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L301" s="6" t="n">
+        <v/>
+      </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N301" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O301" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="302">
@@ -17343,15 +19477,31 @@
       <c r="G302" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H302" s="6" t="inlineStr"/>
-      <c r="I302" s="6" t="inlineStr"/>
-      <c r="J302" s="6" t="inlineStr"/>
-      <c r="K302" s="6" t="inlineStr"/>
-      <c r="L302" s="6" t="inlineStr"/>
+      <c r="H302" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I302" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J302" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K302" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L302" s="6" t="n">
+        <v/>
+      </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N302" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O302" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="303">
@@ -17410,6 +19560,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N303" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O303" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -17467,6 +19623,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N304" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O304" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -17524,6 +19686,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N305" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O305" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -17581,6 +19749,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N306" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O306" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -17638,6 +19812,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N307" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O307" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -17695,6 +19875,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N308" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O308" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -17752,6 +19938,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N309" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O309" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -17809,6 +20001,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N310" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O310" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -17866,6 +20064,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N311" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O311" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -17923,6 +20127,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N312" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O312" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -17980,6 +20190,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N313" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O313" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -18037,6 +20253,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N314" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O314" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -18094,6 +20316,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N315" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O315" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -18151,6 +20379,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N316" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O316" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -18208,6 +20442,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N317" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O317" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -18265,6 +20505,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N318" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O318" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -18322,6 +20568,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N319" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O319" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -18379,6 +20631,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N320" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O320" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -18436,6 +20694,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N321" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O321" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -18471,15 +20735,31 @@
       <c r="G322" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="H322" s="6" t="inlineStr"/>
-      <c r="I322" s="6" t="inlineStr"/>
-      <c r="J322" s="6" t="inlineStr"/>
-      <c r="K322" s="6" t="inlineStr"/>
-      <c r="L322" s="6" t="inlineStr"/>
+      <c r="H322" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I322" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J322" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K322" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L322" s="6" t="n">
+        <v/>
+      </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N322" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O322" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="323">
@@ -18516,15 +20796,33 @@
       <c r="G323" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H323" s="6" t="inlineStr"/>
-      <c r="I323" s="6" t="inlineStr"/>
-      <c r="J323" s="6" t="inlineStr"/>
-      <c r="K323" s="6" t="inlineStr"/>
-      <c r="L323" s="6" t="inlineStr"/>
+      <c r="H323" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I323" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J323" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K323" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L323" s="4" t="n">
+        <v/>
+      </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N323" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O323" s="3" t="n">
+        <v>12.67</v>
       </c>
     </row>
     <row r="324">
@@ -18583,6 +20881,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N324" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O324" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -18640,6 +20944,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N325" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O325" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -18675,15 +20985,33 @@
       <c r="G326" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H326" s="6" t="inlineStr"/>
-      <c r="I326" s="6" t="inlineStr"/>
-      <c r="J326" s="6" t="inlineStr"/>
-      <c r="K326" s="6" t="inlineStr"/>
-      <c r="L326" s="6" t="inlineStr"/>
+      <c r="H326" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K326" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L326" s="4" t="n">
+        <v/>
+      </c>
       <c r="M326" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N326" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O326" s="3" t="n">
+        <v>12.67</v>
       </c>
     </row>
     <row r="327">
@@ -18720,15 +21048,31 @@
       <c r="G327" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H327" s="6" t="inlineStr"/>
-      <c r="I327" s="6" t="inlineStr"/>
-      <c r="J327" s="6" t="inlineStr"/>
-      <c r="K327" s="6" t="inlineStr"/>
-      <c r="L327" s="6" t="inlineStr"/>
+      <c r="H327" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I327" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J327" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K327" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L327" s="6" t="n">
+        <v/>
+      </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N327" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O327" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="328">
@@ -18787,6 +21131,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N328" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O328" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -18844,6 +21194,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N329" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O329" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -18879,15 +21235,31 @@
       <c r="G330" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H330" s="6" t="inlineStr"/>
-      <c r="I330" s="6" t="inlineStr"/>
-      <c r="J330" s="6" t="inlineStr"/>
-      <c r="K330" s="6" t="inlineStr"/>
-      <c r="L330" s="6" t="inlineStr"/>
+      <c r="H330" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I330" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J330" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K330" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L330" s="6" t="n">
+        <v/>
+      </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N330" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O330" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="331">
@@ -18946,6 +21318,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N331" s="3" t="n">
+        <v>-1700</v>
+      </c>
+      <c r="O331" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -19003,6 +21381,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N332" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O332" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -19038,15 +21422,31 @@
       <c r="G333" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H333" s="6" t="inlineStr"/>
-      <c r="I333" s="6" t="inlineStr"/>
-      <c r="J333" s="6" t="inlineStr"/>
-      <c r="K333" s="6" t="inlineStr"/>
-      <c r="L333" s="6" t="inlineStr"/>
+      <c r="H333" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I333" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J333" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K333" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L333" s="6" t="n">
+        <v/>
+      </c>
       <c r="M333" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N333" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O333" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="334">
@@ -19083,15 +21483,33 @@
       <c r="G334" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H334" s="6" t="inlineStr"/>
-      <c r="I334" s="6" t="inlineStr"/>
-      <c r="J334" s="6" t="inlineStr"/>
-      <c r="K334" s="6" t="inlineStr"/>
-      <c r="L334" s="6" t="inlineStr"/>
+      <c r="H334" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K334" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L334" s="4" t="n">
+        <v/>
+      </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N334" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O334" s="3" t="n">
+        <v>13.1</v>
       </c>
     </row>
     <row r="335">
@@ -19128,15 +21546,33 @@
       <c r="G335" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="H335" s="6" t="inlineStr"/>
-      <c r="I335" s="6" t="inlineStr"/>
-      <c r="J335" s="6" t="inlineStr"/>
-      <c r="K335" s="6" t="inlineStr"/>
-      <c r="L335" s="6" t="inlineStr"/>
+      <c r="H335" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I335" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K335" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L335" s="4" t="n">
+        <v/>
+      </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N335" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O335" s="3" t="n">
+        <v>11.52</v>
       </c>
     </row>
     <row r="336">
@@ -19173,15 +21609,33 @@
       <c r="G336" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H336" s="6" t="inlineStr"/>
-      <c r="I336" s="6" t="inlineStr"/>
-      <c r="J336" s="6" t="inlineStr"/>
-      <c r="K336" s="6" t="inlineStr"/>
-      <c r="L336" s="6" t="inlineStr"/>
+      <c r="H336" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K336" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L336" s="4" t="n">
+        <v/>
+      </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N336" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O336" s="3" t="n">
+        <v>12.26</v>
       </c>
     </row>
     <row r="337">
@@ -19218,15 +21672,33 @@
       <c r="G337" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H337" s="6" t="inlineStr"/>
-      <c r="I337" s="6" t="inlineStr"/>
-      <c r="J337" s="6" t="inlineStr"/>
-      <c r="K337" s="6" t="inlineStr"/>
-      <c r="L337" s="6" t="inlineStr"/>
+      <c r="H337" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I337" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L337" s="4" t="n">
+        <v/>
+      </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N337" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O337" s="3" t="n">
+        <v>12.26</v>
       </c>
     </row>
     <row r="338">
@@ -19263,15 +21735,31 @@
       <c r="G338" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H338" s="6" t="inlineStr"/>
-      <c r="I338" s="6" t="inlineStr"/>
-      <c r="J338" s="6" t="inlineStr"/>
-      <c r="K338" s="6" t="inlineStr"/>
-      <c r="L338" s="6" t="inlineStr"/>
+      <c r="H338" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I338" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J338" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K338" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L338" s="6" t="n">
+        <v/>
+      </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N338" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O338" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="339">
@@ -19308,15 +21796,31 @@
       <c r="G339" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H339" s="6" t="inlineStr"/>
-      <c r="I339" s="6" t="inlineStr"/>
-      <c r="J339" s="6" t="inlineStr"/>
-      <c r="K339" s="6" t="inlineStr"/>
-      <c r="L339" s="6" t="inlineStr"/>
+      <c r="H339" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I339" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J339" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K339" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L339" s="6" t="n">
+        <v/>
+      </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N339" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O339" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="340">
@@ -19353,15 +21857,31 @@
       <c r="G340" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H340" s="6" t="inlineStr"/>
-      <c r="I340" s="6" t="inlineStr"/>
-      <c r="J340" s="6" t="inlineStr"/>
-      <c r="K340" s="6" t="inlineStr"/>
-      <c r="L340" s="6" t="inlineStr"/>
+      <c r="H340" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I340" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J340" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K340" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L340" s="6" t="n">
+        <v/>
+      </c>
       <c r="M340" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N340" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O340" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="341">
@@ -19398,15 +21918,33 @@
       <c r="G341" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H341" s="6" t="inlineStr"/>
-      <c r="I341" s="6" t="inlineStr"/>
-      <c r="J341" s="6" t="inlineStr"/>
-      <c r="K341" s="6" t="inlineStr"/>
-      <c r="L341" s="6" t="inlineStr"/>
+      <c r="H341" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I341" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K341" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L341" s="4" t="n">
+        <v/>
+      </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N341" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O341" s="3" t="n">
+        <v>12.67</v>
       </c>
     </row>
     <row r="342">
@@ -19443,15 +21981,31 @@
       <c r="G342" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H342" s="6" t="inlineStr"/>
-      <c r="I342" s="6" t="inlineStr"/>
-      <c r="J342" s="6" t="inlineStr"/>
-      <c r="K342" s="6" t="inlineStr"/>
-      <c r="L342" s="6" t="inlineStr"/>
+      <c r="H342" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I342" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J342" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K342" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L342" s="6" t="n">
+        <v/>
+      </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N342" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O342" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="343">
@@ -19510,6 +22064,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N343" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O343" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -19567,6 +22127,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N344" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O344" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -19624,6 +22190,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N345" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O345" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -19681,6 +22253,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N346" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O346" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -19738,6 +22316,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N347" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O347" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -19795,6 +22379,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N348" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O348" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -19852,6 +22442,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N349" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O349" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -19887,15 +22483,31 @@
       <c r="G350" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="H350" s="6" t="inlineStr"/>
-      <c r="I350" s="6" t="inlineStr"/>
-      <c r="J350" s="6" t="inlineStr"/>
-      <c r="K350" s="6" t="inlineStr"/>
-      <c r="L350" s="6" t="inlineStr"/>
+      <c r="H350" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I350" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J350" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K350" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L350" s="6" t="n">
+        <v/>
+      </c>
       <c r="M350" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N350" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O350" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="351">
@@ -19954,6 +22566,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N351" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O351" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -20011,6 +22629,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N352" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O352" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -20068,6 +22692,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N353" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O353" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -20125,6 +22755,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N354" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O354" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -20160,15 +22796,33 @@
       <c r="G355" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H355" s="6" t="inlineStr"/>
-      <c r="I355" s="6" t="inlineStr"/>
-      <c r="J355" s="6" t="inlineStr"/>
-      <c r="K355" s="6" t="inlineStr"/>
-      <c r="L355" s="6" t="inlineStr"/>
+      <c r="H355" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I355" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K355" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L355" s="4" t="n">
+        <v/>
+      </c>
       <c r="M355" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N355" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O355" s="3" t="n">
+        <v>11.18</v>
       </c>
     </row>
     <row r="356">
@@ -20227,6 +22881,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N356" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O356" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -20284,6 +22944,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N357" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O357" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -20341,6 +23007,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N358" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O358" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -20376,15 +23048,33 @@
       <c r="G359" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H359" s="6" t="inlineStr"/>
-      <c r="I359" s="6" t="inlineStr"/>
-      <c r="J359" s="6" t="inlineStr"/>
-      <c r="K359" s="6" t="inlineStr"/>
-      <c r="L359" s="6" t="inlineStr"/>
+      <c r="H359" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I359" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J359" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K359" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L359" s="4" t="n">
+        <v/>
+      </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N359" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O359" s="3" t="n">
+        <v>12.26</v>
       </c>
     </row>
     <row r="360">
@@ -20443,6 +23133,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N360" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O360" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -20478,15 +23174,31 @@
       <c r="G361" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H361" s="6" t="inlineStr"/>
-      <c r="I361" s="6" t="inlineStr"/>
-      <c r="J361" s="6" t="inlineStr"/>
-      <c r="K361" s="6" t="inlineStr"/>
-      <c r="L361" s="6" t="inlineStr"/>
+      <c r="H361" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I361" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J361" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K361" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L361" s="6" t="n">
+        <v/>
+      </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N361" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O361" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="362">
@@ -20545,6 +23257,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N362" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O362" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -20602,6 +23320,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N363" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O363" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -20659,6 +23383,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N364" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O364" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -20694,15 +23424,31 @@
       <c r="G365" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="H365" s="6" t="inlineStr"/>
-      <c r="I365" s="6" t="inlineStr"/>
-      <c r="J365" s="6" t="inlineStr"/>
-      <c r="K365" s="6" t="inlineStr"/>
-      <c r="L365" s="6" t="inlineStr"/>
+      <c r="H365" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I365" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J365" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K365" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L365" s="6" t="n">
+        <v/>
+      </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N365" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O365" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="366">
@@ -20761,6 +23507,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N366" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O366" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -20818,6 +23570,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N367" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O367" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -20875,6 +23633,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N368" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O368" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -20932,6 +23696,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N369" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O369" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -20989,6 +23759,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N370" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O370" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -21046,6 +23822,12 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N371" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O371" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -21103,6 +23885,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N372" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O372" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -21160,6 +23948,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N373" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O373" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -21217,6 +24011,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N374" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O374" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -21274,6 +24074,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N375" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O375" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -21331,6 +24137,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N376" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O376" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -21388,6 +24200,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N377" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O377" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -21423,15 +24241,33 @@
       <c r="G378" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H378" s="6" t="inlineStr"/>
-      <c r="I378" s="6" t="inlineStr"/>
-      <c r="J378" s="6" t="inlineStr"/>
-      <c r="K378" s="6" t="inlineStr"/>
-      <c r="L378" s="6" t="inlineStr"/>
+      <c r="H378" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I378" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J378" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K378" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L378" s="4" t="n">
+        <v/>
+      </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N378" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O378" s="3" t="n">
+        <v>11.88</v>
       </c>
     </row>
     <row r="379">
@@ -21468,15 +24304,33 @@
       <c r="G379" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H379" s="6" t="inlineStr"/>
-      <c r="I379" s="6" t="inlineStr"/>
-      <c r="J379" s="6" t="inlineStr"/>
-      <c r="K379" s="6" t="inlineStr"/>
-      <c r="L379" s="6" t="inlineStr"/>
+      <c r="H379" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I379" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K379" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L379" s="4" t="n">
+        <v/>
+      </c>
       <c r="M379" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N379" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O379" s="3" t="n">
+        <v>13.57</v>
       </c>
     </row>
     <row r="380">
@@ -21535,6 +24389,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N380" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O380" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -21570,15 +24430,31 @@
       <c r="G381" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H381" s="6" t="inlineStr"/>
-      <c r="I381" s="6" t="inlineStr"/>
-      <c r="J381" s="6" t="inlineStr"/>
-      <c r="K381" s="6" t="inlineStr"/>
-      <c r="L381" s="6" t="inlineStr"/>
+      <c r="H381" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I381" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J381" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K381" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L381" s="6" t="n">
+        <v/>
+      </c>
       <c r="M381" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N381" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O381" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="382">
@@ -21637,6 +24513,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N382" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O382" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -21694,6 +24576,12 @@
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N383" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O383" s="3" t="n">
+        <v>14.07</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -21751,6 +24639,12 @@
           <t>Odd Lay 2x2 (13.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N384" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O384" s="3" t="n">
+        <v>15.83</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -21786,15 +24680,31 @@
       <c r="G385" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H385" s="6" t="inlineStr"/>
-      <c r="I385" s="6" t="inlineStr"/>
-      <c r="J385" s="6" t="inlineStr"/>
-      <c r="K385" s="6" t="inlineStr"/>
-      <c r="L385" s="6" t="inlineStr"/>
+      <c r="H385" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I385" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J385" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K385" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L385" s="6" t="n">
+        <v/>
+      </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N385" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O385" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="386">
@@ -21853,6 +24763,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N386" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O386" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -21910,6 +24826,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N387" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O387" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -21967,6 +24889,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N388" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O388" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -22024,6 +24952,12 @@
           <t>Odd Lay 2x2 (12.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N389" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O389" s="3" t="n">
+        <v>16.52</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -22059,15 +24993,31 @@
       <c r="G390" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="H390" s="6" t="inlineStr"/>
-      <c r="I390" s="6" t="inlineStr"/>
-      <c r="J390" s="6" t="inlineStr"/>
-      <c r="K390" s="6" t="inlineStr"/>
-      <c r="L390" s="6" t="inlineStr"/>
+      <c r="H390" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I390" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J390" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K390" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L390" s="6" t="n">
+        <v/>
+      </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N390" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O390" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="391">
@@ -22126,6 +25076,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N391" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O391" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -22183,6 +25139,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N392" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O392" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -22218,15 +25180,31 @@
       <c r="G393" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="H393" s="6" t="inlineStr"/>
-      <c r="I393" s="6" t="inlineStr"/>
-      <c r="J393" s="6" t="inlineStr"/>
-      <c r="K393" s="6" t="inlineStr"/>
-      <c r="L393" s="6" t="inlineStr"/>
+      <c r="H393" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I393" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J393" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K393" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L393" s="6" t="n">
+        <v/>
+      </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N393" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O393" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="394">
@@ -22263,15 +25241,31 @@
       <c r="G394" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H394" s="6" t="inlineStr"/>
-      <c r="I394" s="6" t="inlineStr"/>
-      <c r="J394" s="6" t="inlineStr"/>
-      <c r="K394" s="6" t="inlineStr"/>
-      <c r="L394" s="6" t="inlineStr"/>
+      <c r="H394" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I394" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J394" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K394" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L394" s="6" t="n">
+        <v/>
+      </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N394" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O394" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="395">
@@ -22330,6 +25324,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N395" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O395" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -22387,6 +25387,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N396" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O396" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -22444,6 +25450,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N397" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O397" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -22479,15 +25491,33 @@
       <c r="G398" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H398" s="6" t="inlineStr"/>
-      <c r="I398" s="6" t="inlineStr"/>
-      <c r="J398" s="6" t="inlineStr"/>
-      <c r="K398" s="6" t="inlineStr"/>
-      <c r="L398" s="6" t="inlineStr"/>
+      <c r="H398" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I398" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K398" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L398" s="4" t="n">
+        <v/>
+      </c>
       <c r="M398" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N398" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O398" s="3" t="n">
+        <v>13.57</v>
       </c>
     </row>
     <row r="399">
@@ -22546,6 +25576,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N399" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O399" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -22603,6 +25639,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N400" s="3" t="n">
+        <v>-1600</v>
+      </c>
+      <c r="O400" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -22660,6 +25702,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N401" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O401" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -22717,6 +25765,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N402" s="3" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="O402" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -22752,15 +25806,33 @@
       <c r="G403" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="H403" s="6" t="inlineStr"/>
-      <c r="I403" s="6" t="inlineStr"/>
-      <c r="J403" s="6" t="inlineStr"/>
-      <c r="K403" s="6" t="inlineStr"/>
-      <c r="L403" s="6" t="inlineStr"/>
+      <c r="H403" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I403" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J403" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K403" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L403" s="4" t="n">
+        <v/>
+      </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N403" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O403" s="3" t="n">
+        <v>15.2</v>
       </c>
     </row>
     <row r="404">
@@ -22797,15 +25869,31 @@
       <c r="G404" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H404" s="6" t="inlineStr"/>
-      <c r="I404" s="6" t="inlineStr"/>
-      <c r="J404" s="6" t="inlineStr"/>
-      <c r="K404" s="6" t="inlineStr"/>
-      <c r="L404" s="6" t="inlineStr"/>
+      <c r="H404" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I404" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J404" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K404" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L404" s="6" t="n">
+        <v/>
+      </c>
       <c r="M404" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N404" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O404" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="405">
@@ -22842,15 +25930,31 @@
       <c r="G405" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="H405" s="6" t="inlineStr"/>
-      <c r="I405" s="6" t="inlineStr"/>
-      <c r="J405" s="6" t="inlineStr"/>
-      <c r="K405" s="6" t="inlineStr"/>
-      <c r="L405" s="6" t="inlineStr"/>
+      <c r="H405" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I405" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J405" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K405" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L405" s="6" t="n">
+        <v/>
+      </c>
       <c r="M405" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N405" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O405" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="406">
@@ -22887,15 +25991,33 @@
       <c r="G406" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H406" s="6" t="inlineStr"/>
-      <c r="I406" s="6" t="inlineStr"/>
-      <c r="J406" s="6" t="inlineStr"/>
-      <c r="K406" s="6" t="inlineStr"/>
-      <c r="L406" s="6" t="inlineStr"/>
+      <c r="H406" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I406" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J406" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K406" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L406" s="4" t="n">
+        <v/>
+      </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N406" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O406" s="3" t="n">
+        <v>12.67</v>
       </c>
     </row>
     <row r="407">
@@ -22932,15 +26054,33 @@
       <c r="G407" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H407" s="6" t="inlineStr"/>
-      <c r="I407" s="6" t="inlineStr"/>
-      <c r="J407" s="6" t="inlineStr"/>
-      <c r="K407" s="6" t="inlineStr"/>
-      <c r="L407" s="6" t="inlineStr"/>
+      <c r="H407" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I407" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J407" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K407" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L407" s="4" t="n">
+        <v/>
+      </c>
       <c r="M407" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N407" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O407" s="3" t="n">
+        <v>11.88</v>
       </c>
     </row>
     <row r="408">
@@ -22999,6 +26139,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N408" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O408" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -23056,6 +26202,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N409" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O409" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -23113,6 +26265,12 @@
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N410" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O410" s="3" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -23148,15 +26306,33 @@
       <c r="G411" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H411" s="6" t="inlineStr"/>
-      <c r="I411" s="6" t="inlineStr"/>
-      <c r="J411" s="6" t="inlineStr"/>
-      <c r="K411" s="6" t="inlineStr"/>
-      <c r="L411" s="6" t="inlineStr"/>
+      <c r="H411" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I411" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J411" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K411" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L411" s="4" t="n">
+        <v/>
+      </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N411" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O411" s="3" t="n">
+        <v>11.88</v>
       </c>
     </row>
     <row r="412">
@@ -23215,6 +26391,12 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N412" s="3" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="O412" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -23250,15 +26432,31 @@
       <c r="G413" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H413" s="6" t="inlineStr"/>
-      <c r="I413" s="6" t="inlineStr"/>
-      <c r="J413" s="6" t="inlineStr"/>
-      <c r="K413" s="6" t="inlineStr"/>
-      <c r="L413" s="6" t="inlineStr"/>
+      <c r="H413" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I413" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J413" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K413" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L413" s="6" t="n">
+        <v/>
+      </c>
       <c r="M413" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O413" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="414">
@@ -23317,6 +26515,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N414" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O414" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -23374,6 +26578,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N415" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O415" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -23431,6 +26641,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N416" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O416" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -23488,6 +26704,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N417" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O417" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -23523,15 +26745,31 @@
       <c r="G418" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H418" s="6" t="inlineStr"/>
-      <c r="I418" s="6" t="inlineStr"/>
-      <c r="J418" s="6" t="inlineStr"/>
-      <c r="K418" s="6" t="inlineStr"/>
-      <c r="L418" s="6" t="inlineStr"/>
+      <c r="H418" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I418" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J418" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K418" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L418" s="6" t="n">
+        <v/>
+      </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N418" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O418" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="419">
@@ -23568,15 +26806,31 @@
       <c r="G419" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H419" s="6" t="inlineStr"/>
-      <c r="I419" s="6" t="inlineStr"/>
-      <c r="J419" s="6" t="inlineStr"/>
-      <c r="K419" s="6" t="inlineStr"/>
-      <c r="L419" s="6" t="inlineStr"/>
+      <c r="H419" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I419" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J419" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K419" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L419" s="6" t="n">
+        <v/>
+      </c>
       <c r="M419" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N419" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O419" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="420">
@@ -23613,15 +26867,31 @@
       <c r="G420" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H420" s="6" t="inlineStr"/>
-      <c r="I420" s="6" t="inlineStr"/>
-      <c r="J420" s="6" t="inlineStr"/>
-      <c r="K420" s="6" t="inlineStr"/>
-      <c r="L420" s="6" t="inlineStr"/>
+      <c r="H420" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I420" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J420" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K420" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L420" s="6" t="n">
+        <v/>
+      </c>
       <c r="M420" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N420" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O420" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="421">
@@ -23658,15 +26928,31 @@
       <c r="G421" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H421" s="6" t="inlineStr"/>
-      <c r="I421" s="6" t="inlineStr"/>
-      <c r="J421" s="6" t="inlineStr"/>
-      <c r="K421" s="6" t="inlineStr"/>
-      <c r="L421" s="6" t="inlineStr"/>
+      <c r="H421" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I421" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J421" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K421" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L421" s="6" t="n">
+        <v/>
+      </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N421" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O421" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="422">
@@ -23725,6 +27011,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N422" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O422" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -23760,15 +27052,31 @@
       <c r="G423" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H423" s="6" t="inlineStr"/>
-      <c r="I423" s="6" t="inlineStr"/>
-      <c r="J423" s="6" t="inlineStr"/>
-      <c r="K423" s="6" t="inlineStr"/>
-      <c r="L423" s="6" t="inlineStr"/>
+      <c r="H423" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I423" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J423" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K423" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L423" s="6" t="n">
+        <v/>
+      </c>
       <c r="M423" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N423" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O423" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="424">
@@ -23805,15 +27113,31 @@
       <c r="G424" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H424" s="6" t="inlineStr"/>
-      <c r="I424" s="6" t="inlineStr"/>
-      <c r="J424" s="6" t="inlineStr"/>
-      <c r="K424" s="6" t="inlineStr"/>
-      <c r="L424" s="6" t="inlineStr"/>
+      <c r="H424" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I424" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J424" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K424" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L424" s="6" t="n">
+        <v/>
+      </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N424" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O424" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="425">
@@ -23872,6 +27196,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N425" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O425" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -23929,6 +27259,12 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N426" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O426" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -23986,6 +27322,12 @@
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N427" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O427" s="3" t="n">
+        <v>11.52</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -24043,6 +27385,12 @@
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N428" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O428" s="3" t="n">
+        <v>11.18</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -24100,6 +27448,12 @@
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N429" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O429" s="3" t="n">
+        <v>12.67</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -24157,6 +27511,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N430" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O430" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -24192,15 +27552,33 @@
       <c r="G431" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H431" s="6" t="inlineStr"/>
-      <c r="I431" s="6" t="inlineStr"/>
-      <c r="J431" s="6" t="inlineStr"/>
-      <c r="K431" s="6" t="inlineStr"/>
-      <c r="L431" s="6" t="inlineStr"/>
+      <c r="H431" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I431" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J431" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K431" s="4" t="n">
+        <v/>
+      </c>
+      <c r="L431" s="4" t="n">
+        <v/>
+      </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N431" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O431" s="3" t="n">
+        <v>12.26</v>
       </c>
     </row>
     <row r="432">
@@ -24259,6 +27637,12 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N432" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O432" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -24316,6 +27700,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N433" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O433" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -24373,6 +27763,12 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
+      <c r="N434" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O434" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -24408,15 +27804,31 @@
       <c r="G435" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H435" s="6" t="inlineStr"/>
-      <c r="I435" s="6" t="inlineStr"/>
-      <c r="J435" s="6" t="inlineStr"/>
-      <c r="K435" s="6" t="inlineStr"/>
-      <c r="L435" s="6" t="inlineStr"/>
+      <c r="H435" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I435" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J435" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K435" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L435" s="6" t="n">
+        <v/>
+      </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N435" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O435" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="436">
@@ -24453,15 +27865,31 @@
       <c r="G436" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H436" s="6" t="inlineStr"/>
-      <c r="I436" s="6" t="inlineStr"/>
-      <c r="J436" s="6" t="inlineStr"/>
-      <c r="K436" s="6" t="inlineStr"/>
-      <c r="L436" s="6" t="inlineStr"/>
+      <c r="H436" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I436" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J436" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K436" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L436" s="6" t="n">
+        <v/>
+      </c>
       <c r="M436" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N436" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O436" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="437">
@@ -24498,15 +27926,31 @@
       <c r="G437" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H437" s="6" t="inlineStr"/>
-      <c r="I437" s="6" t="inlineStr"/>
-      <c r="J437" s="6" t="inlineStr"/>
-      <c r="K437" s="6" t="inlineStr"/>
-      <c r="L437" s="6" t="inlineStr"/>
+      <c r="H437" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I437" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J437" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K437" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L437" s="6" t="n">
+        <v/>
+      </c>
       <c r="M437" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N437" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O437" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="438">
@@ -24543,15 +27987,31 @@
       <c r="G438" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H438" s="6" t="inlineStr"/>
-      <c r="I438" s="6" t="inlineStr"/>
-      <c r="J438" s="6" t="inlineStr"/>
-      <c r="K438" s="6" t="inlineStr"/>
-      <c r="L438" s="6" t="inlineStr"/>
+      <c r="H438" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I438" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J438" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K438" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L438" s="6" t="n">
+        <v/>
+      </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N438" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O438" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="439">
@@ -24588,15 +28048,31 @@
       <c r="G439" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H439" s="6" t="inlineStr"/>
-      <c r="I439" s="6" t="inlineStr"/>
-      <c r="J439" s="6" t="inlineStr"/>
-      <c r="K439" s="6" t="inlineStr"/>
-      <c r="L439" s="6" t="inlineStr"/>
+      <c r="H439" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I439" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J439" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K439" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L439" s="6" t="n">
+        <v/>
+      </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N439" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O439" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="440">
@@ -24633,15 +28109,31 @@
       <c r="G440" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H440" s="6" t="inlineStr"/>
-      <c r="I440" s="6" t="inlineStr"/>
-      <c r="J440" s="6" t="inlineStr"/>
-      <c r="K440" s="6" t="inlineStr"/>
-      <c r="L440" s="6" t="inlineStr"/>
+      <c r="H440" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I440" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J440" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K440" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L440" s="6" t="n">
+        <v/>
+      </c>
       <c r="M440" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N440" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O440" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="441">
@@ -24678,15 +28170,31 @@
       <c r="G441" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H441" s="6" t="inlineStr"/>
-      <c r="I441" s="6" t="inlineStr"/>
-      <c r="J441" s="6" t="inlineStr"/>
-      <c r="K441" s="6" t="inlineStr"/>
-      <c r="L441" s="6" t="inlineStr"/>
+      <c r="H441" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I441" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J441" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K441" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L441" s="6" t="n">
+        <v/>
+      </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N441" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O441" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="442">
@@ -24723,15 +28231,31 @@
       <c r="G442" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H442" s="6" t="inlineStr"/>
-      <c r="I442" s="6" t="inlineStr"/>
-      <c r="J442" s="6" t="inlineStr"/>
-      <c r="K442" s="6" t="inlineStr"/>
-      <c r="L442" s="6" t="inlineStr"/>
+      <c r="H442" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I442" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J442" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K442" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L442" s="6" t="n">
+        <v/>
+      </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N442" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O442" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="443">
@@ -24768,15 +28292,31 @@
       <c r="G443" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H443" s="6" t="inlineStr"/>
-      <c r="I443" s="6" t="inlineStr"/>
-      <c r="J443" s="6" t="inlineStr"/>
-      <c r="K443" s="6" t="inlineStr"/>
-      <c r="L443" s="6" t="inlineStr"/>
+      <c r="H443" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I443" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J443" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K443" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L443" s="6" t="n">
+        <v/>
+      </c>
       <c r="M443" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N443" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O443" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="444">
@@ -24813,15 +28353,31 @@
       <c r="G444" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="H444" s="6" t="inlineStr"/>
-      <c r="I444" s="6" t="inlineStr"/>
-      <c r="J444" s="6" t="inlineStr"/>
-      <c r="K444" s="6" t="inlineStr"/>
-      <c r="L444" s="6" t="inlineStr"/>
+      <c r="H444" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I444" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J444" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K444" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L444" s="6" t="n">
+        <v/>
+      </c>
       <c r="M444" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N444" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O444" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="445">
@@ -24858,15 +28414,31 @@
       <c r="G445" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H445" s="6" t="inlineStr"/>
-      <c r="I445" s="6" t="inlineStr"/>
-      <c r="J445" s="6" t="inlineStr"/>
-      <c r="K445" s="6" t="inlineStr"/>
-      <c r="L445" s="6" t="inlineStr"/>
+      <c r="H445" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I445" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J445" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K445" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L445" s="6" t="n">
+        <v/>
+      </c>
       <c r="M445" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N445" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O445" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="446">
@@ -24903,15 +28475,31 @@
       <c r="G446" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H446" s="6" t="inlineStr"/>
-      <c r="I446" s="6" t="inlineStr"/>
-      <c r="J446" s="6" t="inlineStr"/>
-      <c r="K446" s="6" t="inlineStr"/>
-      <c r="L446" s="6" t="inlineStr"/>
+      <c r="H446" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I446" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J446" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K446" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L446" s="6" t="n">
+        <v/>
+      </c>
       <c r="M446" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N446" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O446" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="447">
@@ -24948,15 +28536,31 @@
       <c r="G447" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H447" s="6" t="inlineStr"/>
-      <c r="I447" s="6" t="inlineStr"/>
-      <c r="J447" s="6" t="inlineStr"/>
-      <c r="K447" s="6" t="inlineStr"/>
-      <c r="L447" s="6" t="inlineStr"/>
+      <c r="H447" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I447" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J447" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K447" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L447" s="6" t="n">
+        <v/>
+      </c>
       <c r="M447" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N447" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O447" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="448">
@@ -24993,15 +28597,31 @@
       <c r="G448" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H448" s="6" t="inlineStr"/>
-      <c r="I448" s="6" t="inlineStr"/>
-      <c r="J448" s="6" t="inlineStr"/>
-      <c r="K448" s="6" t="inlineStr"/>
-      <c r="L448" s="6" t="inlineStr"/>
+      <c r="H448" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I448" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J448" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K448" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L448" s="6" t="n">
+        <v/>
+      </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N448" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O448" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="449">
@@ -25038,15 +28658,31 @@
       <c r="G449" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H449" s="6" t="inlineStr"/>
-      <c r="I449" s="6" t="inlineStr"/>
-      <c r="J449" s="6" t="inlineStr"/>
-      <c r="K449" s="6" t="inlineStr"/>
-      <c r="L449" s="6" t="inlineStr"/>
+      <c r="H449" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I449" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J449" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K449" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L449" s="6" t="n">
+        <v/>
+      </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N449" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O449" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="450">
@@ -25083,15 +28719,31 @@
       <c r="G450" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H450" s="6" t="inlineStr"/>
-      <c r="I450" s="6" t="inlineStr"/>
-      <c r="J450" s="6" t="inlineStr"/>
-      <c r="K450" s="6" t="inlineStr"/>
-      <c r="L450" s="6" t="inlineStr"/>
+      <c r="H450" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I450" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J450" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K450" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L450" s="6" t="n">
+        <v/>
+      </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N450" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O450" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="451">
@@ -25128,15 +28780,31 @@
       <c r="G451" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H451" s="6" t="inlineStr"/>
-      <c r="I451" s="6" t="inlineStr"/>
-      <c r="J451" s="6" t="inlineStr"/>
-      <c r="K451" s="6" t="inlineStr"/>
-      <c r="L451" s="6" t="inlineStr"/>
+      <c r="H451" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I451" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J451" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K451" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L451" s="6" t="n">
+        <v/>
+      </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
+      </c>
+      <c r="N451" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O451" s="3" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Backtest_Lay_2x2_Agosto_2026.xlsx
+++ b/Backtest_Lay_2x2_Agosto_2026.xlsx
@@ -11439,31 +11439,33 @@
       <c r="G174" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H174" s="6" t="n">
+      <c r="H174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K174" s="4" t="n">
         <v/>
       </c>
-      <c r="I174" s="6" t="n">
+      <c r="L174" s="4" t="n">
         <v/>
       </c>
-      <c r="J174" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K174" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L174" s="6" t="n">
-        <v/>
-      </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N174" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O174" s="3" t="n">
-        <v/>
+        <v>11.88</v>
       </c>
     </row>
     <row r="175">
@@ -11941,31 +11943,33 @@
       <c r="G182" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H182" s="6" t="n">
+      <c r="H182" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="n">
         <v/>
       </c>
-      <c r="I182" s="6" t="n">
+      <c r="L182" s="4" t="n">
         <v/>
       </c>
-      <c r="J182" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K182" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L182" s="6" t="n">
-        <v/>
-      </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N182" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O182" s="3" t="n">
-        <v/>
+        <v>12.67</v>
       </c>
     </row>
     <row r="183">
@@ -12695,31 +12699,33 @@
       <c r="G194" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H194" s="6" t="n">
+      <c r="H194" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K194" s="4" t="n">
         <v/>
       </c>
-      <c r="I194" s="6" t="n">
+      <c r="L194" s="4" t="n">
         <v/>
       </c>
-      <c r="J194" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K194" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L194" s="6" t="n">
-        <v/>
-      </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N194" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O194" s="3" t="n">
-        <v/>
+        <v>11.18</v>
       </c>
     </row>
     <row r="195">
@@ -13071,31 +13077,33 @@
       <c r="G200" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H200" s="6" t="n">
+      <c r="H200" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K200" s="4" t="n">
         <v/>
       </c>
-      <c r="I200" s="6" t="n">
+      <c r="L200" s="4" t="n">
         <v/>
       </c>
-      <c r="J200" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K200" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L200" s="6" t="n">
-        <v/>
-      </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N200" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O200" s="3" t="n">
-        <v/>
+        <v>12.67</v>
       </c>
     </row>
     <row r="201">
@@ -13195,31 +13203,33 @@
       <c r="G202" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H202" s="6" t="n">
+      <c r="H202" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I202" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K202" s="4" t="n">
         <v/>
       </c>
-      <c r="I202" s="6" t="n">
+      <c r="L202" s="4" t="n">
         <v/>
       </c>
-      <c r="J202" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K202" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L202" s="6" t="n">
-        <v/>
-      </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N202" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O202" s="3" t="n">
-        <v/>
+        <v>14.62</v>
       </c>
     </row>
     <row r="203">
@@ -15713,31 +15723,33 @@
       <c r="G242" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H242" s="6" t="n">
+      <c r="H242" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I242" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K242" s="4" t="n">
         <v/>
       </c>
-      <c r="I242" s="6" t="n">
+      <c r="L242" s="4" t="n">
         <v/>
       </c>
-      <c r="J242" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K242" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L242" s="6" t="n">
-        <v/>
-      </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N242" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O242" s="3" t="n">
-        <v/>
+        <v>13.1</v>
       </c>
     </row>
     <row r="243">
@@ -15837,31 +15849,33 @@
       <c r="G244" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H244" s="6" t="n">
+      <c r="H244" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J244" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K244" s="4" t="n">
         <v/>
       </c>
-      <c r="I244" s="6" t="n">
+      <c r="L244" s="4" t="n">
         <v/>
       </c>
-      <c r="J244" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K244" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L244" s="6" t="n">
-        <v/>
-      </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N244" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O244" s="3" t="n">
-        <v/>
+        <v>11.18</v>
       </c>
     </row>
     <row r="245">
@@ -16024,31 +16038,33 @@
       <c r="G247" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H247" s="6" t="n">
+      <c r="H247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I247" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J247" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K247" s="4" t="n">
         <v/>
       </c>
-      <c r="I247" s="6" t="n">
+      <c r="L247" s="4" t="n">
         <v/>
       </c>
-      <c r="J247" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K247" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L247" s="6" t="n">
-        <v/>
-      </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N247" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O247" s="3" t="n">
-        <v/>
+        <v>11.88</v>
       </c>
     </row>
     <row r="248">
@@ -16085,31 +16101,33 @@
       <c r="G248" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H248" s="6" t="n">
+      <c r="H248" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I248" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K248" s="4" t="n">
         <v/>
       </c>
-      <c r="I248" s="6" t="n">
+      <c r="L248" s="4" t="n">
         <v/>
       </c>
-      <c r="J248" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K248" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L248" s="6" t="n">
-        <v/>
-      </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N248" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O248" s="3" t="n">
-        <v/>
+        <v>13.1</v>
       </c>
     </row>
     <row r="249">
@@ -16209,31 +16227,33 @@
       <c r="G250" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H250" s="6" t="n">
+      <c r="H250" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K250" s="4" t="n">
         <v/>
       </c>
-      <c r="I250" s="6" t="n">
+      <c r="L250" s="4" t="n">
         <v/>
       </c>
-      <c r="J250" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K250" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L250" s="6" t="n">
-        <v/>
-      </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N250" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O250" s="3" t="n">
-        <v/>
+        <v>12.26</v>
       </c>
     </row>
     <row r="251">
@@ -18916,31 +18936,33 @@
       <c r="G293" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H293" s="6" t="n">
+      <c r="H293" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I293" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J293" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K293" s="4" t="n">
         <v/>
       </c>
-      <c r="I293" s="6" t="n">
+      <c r="L293" s="4" t="n">
         <v/>
       </c>
-      <c r="J293" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K293" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L293" s="6" t="n">
-        <v/>
-      </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N293" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O293" s="3" t="n">
-        <v/>
+        <v>12.26</v>
       </c>
     </row>
     <row r="294">
@@ -19103,31 +19125,33 @@
       <c r="G296" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H296" s="6" t="n">
+      <c r="H296" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I296" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J296" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K296" s="4" t="n">
         <v/>
       </c>
-      <c r="I296" s="6" t="n">
+      <c r="L296" s="4" t="n">
         <v/>
       </c>
-      <c r="J296" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K296" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L296" s="6" t="n">
-        <v/>
-      </c>
       <c r="M296" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N296" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O296" s="3" t="n">
-        <v/>
+        <v>12.67</v>
       </c>
     </row>
     <row r="297">
@@ -19416,31 +19440,33 @@
       <c r="G301" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H301" s="6" t="n">
+      <c r="H301" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I301" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K301" s="4" t="n">
         <v/>
       </c>
-      <c r="I301" s="6" t="n">
+      <c r="L301" s="4" t="n">
         <v/>
       </c>
-      <c r="J301" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K301" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L301" s="6" t="n">
-        <v/>
-      </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N301" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O301" s="3" t="n">
-        <v/>
+        <v>11.88</v>
       </c>
     </row>
     <row r="302">
@@ -19477,31 +19503,33 @@
       <c r="G302" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H302" s="6" t="n">
+      <c r="H302" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K302" s="4" t="n">
         <v/>
       </c>
-      <c r="I302" s="6" t="n">
+      <c r="L302" s="4" t="n">
         <v/>
       </c>
-      <c r="J302" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K302" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L302" s="6" t="n">
-        <v/>
-      </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N302" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O302" s="3" t="n">
-        <v/>
+        <v>11.88</v>
       </c>
     </row>
     <row r="303">
@@ -20735,31 +20763,33 @@
       <c r="G322" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="H322" s="6" t="n">
+      <c r="H322" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I322" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J322" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K322" s="4" t="n">
         <v/>
       </c>
-      <c r="I322" s="6" t="n">
+      <c r="L322" s="4" t="n">
         <v/>
       </c>
-      <c r="J322" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K322" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L322" s="6" t="n">
-        <v/>
-      </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N322" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O322" s="3" t="n">
-        <v/>
+        <v>15.2</v>
       </c>
     </row>
     <row r="323">
@@ -21048,31 +21078,33 @@
       <c r="G327" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H327" s="6" t="n">
+      <c r="H327" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I327" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J327" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K327" s="4" t="n">
         <v/>
       </c>
-      <c r="I327" s="6" t="n">
+      <c r="L327" s="4" t="n">
         <v/>
       </c>
-      <c r="J327" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K327" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L327" s="6" t="n">
-        <v/>
-      </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N327" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O327" s="3" t="n">
-        <v/>
+        <v>11.88</v>
       </c>
     </row>
     <row r="328">
@@ -21235,31 +21267,33 @@
       <c r="G330" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H330" s="6" t="n">
+      <c r="H330" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I330" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J330" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K330" s="4" t="n">
         <v/>
       </c>
-      <c r="I330" s="6" t="n">
+      <c r="L330" s="4" t="n">
         <v/>
       </c>
-      <c r="J330" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K330" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L330" s="6" t="n">
-        <v/>
-      </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N330" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O330" s="3" t="n">
-        <v/>
+        <v>13.57</v>
       </c>
     </row>
     <row r="331">
@@ -21422,31 +21456,33 @@
       <c r="G333" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H333" s="6" t="n">
+      <c r="H333" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I333" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J333" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K333" s="4" t="n">
         <v/>
       </c>
-      <c r="I333" s="6" t="n">
+      <c r="L333" s="4" t="n">
         <v/>
       </c>
-      <c r="J333" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K333" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L333" s="6" t="n">
-        <v/>
-      </c>
       <c r="M333" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N333" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O333" s="3" t="n">
-        <v/>
+        <v>12.26</v>
       </c>
     </row>
     <row r="334">
@@ -21735,31 +21771,33 @@
       <c r="G338" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H338" s="6" t="n">
+      <c r="H338" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I338" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J338" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K338" s="4" t="n">
         <v/>
       </c>
-      <c r="I338" s="6" t="n">
+      <c r="L338" s="4" t="n">
         <v/>
       </c>
-      <c r="J338" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K338" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L338" s="6" t="n">
-        <v/>
-      </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N338" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O338" s="3" t="n">
-        <v/>
+        <v>13.57</v>
       </c>
     </row>
     <row r="339">
@@ -21796,31 +21834,33 @@
       <c r="G339" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H339" s="6" t="n">
+      <c r="H339" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I339" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J339" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K339" s="4" t="n">
         <v/>
       </c>
-      <c r="I339" s="6" t="n">
+      <c r="L339" s="4" t="n">
         <v/>
       </c>
-      <c r="J339" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K339" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L339" s="6" t="n">
-        <v/>
-      </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N339" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O339" s="3" t="n">
-        <v/>
+        <v>11.88</v>
       </c>
     </row>
     <row r="340">
@@ -21857,31 +21897,33 @@
       <c r="G340" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H340" s="6" t="n">
+      <c r="H340" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I340" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K340" s="4" t="n">
         <v/>
       </c>
-      <c r="I340" s="6" t="n">
+      <c r="L340" s="4" t="n">
         <v/>
       </c>
-      <c r="J340" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K340" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L340" s="6" t="n">
-        <v/>
-      </c>
       <c r="M340" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N340" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O340" s="3" t="n">
-        <v/>
+        <v>12.26</v>
       </c>
     </row>
     <row r="341">
@@ -21981,31 +22023,33 @@
       <c r="G342" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H342" s="6" t="n">
+      <c r="H342" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I342" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J342" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K342" s="4" t="n">
         <v/>
       </c>
-      <c r="I342" s="6" t="n">
+      <c r="L342" s="4" t="n">
         <v/>
       </c>
-      <c r="J342" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K342" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L342" s="6" t="n">
-        <v/>
-      </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N342" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O342" s="3" t="n">
-        <v/>
+        <v>13.1</v>
       </c>
     </row>
     <row r="343">
@@ -22483,31 +22527,33 @@
       <c r="G350" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="H350" s="6" t="n">
+      <c r="H350" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I350" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J350" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K350" s="4" t="n">
         <v/>
       </c>
-      <c r="I350" s="6" t="n">
+      <c r="L350" s="4" t="n">
         <v/>
       </c>
-      <c r="J350" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K350" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L350" s="6" t="n">
-        <v/>
-      </c>
       <c r="M350" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N350" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O350" s="3" t="n">
-        <v/>
+        <v>14.07</v>
       </c>
     </row>
     <row r="351">
@@ -23174,31 +23220,33 @@
       <c r="G361" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H361" s="6" t="n">
+      <c r="H361" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I361" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K361" s="4" t="n">
         <v/>
       </c>
-      <c r="I361" s="6" t="n">
+      <c r="L361" s="4" t="n">
         <v/>
       </c>
-      <c r="J361" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K361" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L361" s="6" t="n">
-        <v/>
-      </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N361" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O361" s="3" t="n">
-        <v/>
+        <v>13.1</v>
       </c>
     </row>
     <row r="362">
@@ -23424,31 +23472,33 @@
       <c r="G365" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="H365" s="6" t="n">
+      <c r="H365" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J365" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K365" s="4" t="n">
         <v/>
       </c>
-      <c r="I365" s="6" t="n">
+      <c r="L365" s="4" t="n">
         <v/>
       </c>
-      <c r="J365" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K365" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L365" s="6" t="n">
-        <v/>
-      </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N365" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O365" s="3" t="n">
-        <v/>
+        <v>11.52</v>
       </c>
     </row>
     <row r="366">
@@ -24430,31 +24480,33 @@
       <c r="G381" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H381" s="6" t="n">
+      <c r="H381" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I381" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J381" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K381" s="4" t="n">
         <v/>
       </c>
-      <c r="I381" s="6" t="n">
+      <c r="L381" s="4" t="n">
         <v/>
       </c>
-      <c r="J381" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K381" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L381" s="6" t="n">
-        <v/>
-      </c>
       <c r="M381" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N381" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O381" s="3" t="n">
-        <v/>
+        <v>11.88</v>
       </c>
     </row>
     <row r="382">
@@ -24680,31 +24732,33 @@
       <c r="G385" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H385" s="6" t="n">
+      <c r="H385" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I385" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J385" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K385" s="4" t="n">
         <v/>
       </c>
-      <c r="I385" s="6" t="n">
+      <c r="L385" s="4" t="n">
         <v/>
       </c>
-      <c r="J385" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K385" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L385" s="6" t="n">
-        <v/>
-      </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N385" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O385" s="3" t="n">
-        <v/>
+        <v>12.67</v>
       </c>
     </row>
     <row r="386">
@@ -24993,31 +25047,33 @@
       <c r="G390" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="H390" s="6" t="n">
+      <c r="H390" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I390" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K390" s="4" t="n">
         <v/>
       </c>
-      <c r="I390" s="6" t="n">
+      <c r="L390" s="4" t="n">
         <v/>
       </c>
-      <c r="J390" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K390" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L390" s="6" t="n">
-        <v/>
-      </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N390" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O390" s="3" t="n">
-        <v/>
+        <v>14.07</v>
       </c>
     </row>
     <row r="391">
@@ -25180,31 +25236,33 @@
       <c r="G393" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="H393" s="6" t="n">
+      <c r="H393" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I393" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J393" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K393" s="4" t="n">
         <v/>
       </c>
-      <c r="I393" s="6" t="n">
+      <c r="L393" s="4" t="n">
         <v/>
       </c>
-      <c r="J393" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K393" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L393" s="6" t="n">
-        <v/>
-      </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N393" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O393" s="3" t="n">
-        <v/>
+        <v>11.52</v>
       </c>
     </row>
     <row r="394">
@@ -25241,31 +25299,33 @@
       <c r="G394" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H394" s="6" t="n">
+      <c r="H394" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I394" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J394" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K394" s="4" t="n">
         <v/>
       </c>
-      <c r="I394" s="6" t="n">
+      <c r="L394" s="4" t="n">
         <v/>
       </c>
-      <c r="J394" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K394" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L394" s="6" t="n">
-        <v/>
-      </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N394" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O394" s="3" t="n">
-        <v/>
+        <v>11.88</v>
       </c>
     </row>
     <row r="395">
@@ -25869,31 +25929,33 @@
       <c r="G404" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H404" s="6" t="n">
+      <c r="H404" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I404" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J404" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K404" s="4" t="n">
         <v/>
       </c>
-      <c r="I404" s="6" t="n">
+      <c r="L404" s="4" t="n">
         <v/>
       </c>
-      <c r="J404" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K404" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L404" s="6" t="n">
-        <v/>
-      </c>
       <c r="M404" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N404" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O404" s="3" t="n">
-        <v/>
+        <v>13.1</v>
       </c>
     </row>
     <row r="405">
@@ -25930,31 +25992,33 @@
       <c r="G405" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="H405" s="6" t="n">
+      <c r="H405" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I405" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J405" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K405" s="4" t="n">
         <v/>
       </c>
-      <c r="I405" s="6" t="n">
+      <c r="L405" s="4" t="n">
         <v/>
       </c>
-      <c r="J405" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K405" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L405" s="6" t="n">
-        <v/>
-      </c>
       <c r="M405" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N405" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O405" s="3" t="n">
-        <v/>
+        <v>14.07</v>
       </c>
     </row>
     <row r="406">
@@ -26432,31 +26496,33 @@
       <c r="G413" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H413" s="6" t="n">
+      <c r="H413" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I413" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J413" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K413" s="4" t="n">
         <v/>
       </c>
-      <c r="I413" s="6" t="n">
+      <c r="L413" s="4" t="n">
         <v/>
       </c>
-      <c r="J413" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K413" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L413" s="6" t="n">
-        <v/>
-      </c>
       <c r="M413" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N413" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O413" s="3" t="n">
-        <v/>
+        <v>13.1</v>
       </c>
     </row>
     <row r="414">
@@ -26745,31 +26811,33 @@
       <c r="G418" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H418" s="6" t="n">
+      <c r="H418" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I418" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J418" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K418" s="4" t="n">
         <v/>
       </c>
-      <c r="I418" s="6" t="n">
+      <c r="L418" s="4" t="n">
         <v/>
       </c>
-      <c r="J418" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K418" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L418" s="6" t="n">
-        <v/>
-      </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N418" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O418" s="3" t="n">
-        <v/>
+        <v>13.57</v>
       </c>
     </row>
     <row r="419">
@@ -26806,31 +26874,33 @@
       <c r="G419" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="H419" s="6" t="n">
+      <c r="H419" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I419" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J419" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K419" s="4" t="n">
         <v/>
       </c>
-      <c r="I419" s="6" t="n">
+      <c r="L419" s="4" t="n">
         <v/>
       </c>
-      <c r="J419" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K419" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L419" s="6" t="n">
-        <v/>
-      </c>
       <c r="M419" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N419" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O419" s="3" t="n">
-        <v/>
+        <v>12.67</v>
       </c>
     </row>
     <row r="420">
@@ -26867,31 +26937,33 @@
       <c r="G420" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H420" s="6" t="n">
+      <c r="H420" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I420" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J420" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K420" s="4" t="n">
         <v/>
       </c>
-      <c r="I420" s="6" t="n">
+      <c r="L420" s="4" t="n">
         <v/>
       </c>
-      <c r="J420" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K420" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L420" s="6" t="n">
-        <v/>
-      </c>
       <c r="M420" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N420" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O420" s="3" t="n">
-        <v/>
+        <v>14.62</v>
       </c>
     </row>
     <row r="421">
@@ -26928,31 +27000,33 @@
       <c r="G421" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H421" s="6" t="n">
+      <c r="H421" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I421" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J421" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K421" s="4" t="n">
         <v/>
       </c>
-      <c r="I421" s="6" t="n">
+      <c r="L421" s="4" t="n">
         <v/>
       </c>
-      <c r="J421" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K421" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L421" s="6" t="n">
-        <v/>
-      </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N421" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O421" s="3" t="n">
-        <v/>
+        <v>12.26</v>
       </c>
     </row>
     <row r="422">
@@ -27052,31 +27126,33 @@
       <c r="G423" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H423" s="6" t="n">
+      <c r="H423" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I423" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J423" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K423" s="4" t="n">
         <v/>
       </c>
-      <c r="I423" s="6" t="n">
+      <c r="L423" s="4" t="n">
         <v/>
       </c>
-      <c r="J423" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K423" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L423" s="6" t="n">
-        <v/>
-      </c>
       <c r="M423" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N423" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O423" s="3" t="n">
-        <v/>
+        <v>13.1</v>
       </c>
     </row>
     <row r="424">
@@ -27113,31 +27189,33 @@
       <c r="G424" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H424" s="6" t="n">
+      <c r="H424" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I424" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K424" s="4" t="n">
         <v/>
       </c>
-      <c r="I424" s="6" t="n">
+      <c r="L424" s="4" t="n">
         <v/>
       </c>
-      <c r="J424" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K424" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L424" s="6" t="n">
-        <v/>
-      </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (18.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N424" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O424" s="3" t="n">
-        <v/>
+        <v>11.18</v>
       </c>
     </row>
     <row r="425">
@@ -27804,31 +27882,33 @@
       <c r="G435" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H435" s="6" t="n">
+      <c r="H435" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I435" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J435" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K435" s="4" t="n">
         <v/>
       </c>
-      <c r="I435" s="6" t="n">
+      <c r="L435" s="4" t="n">
         <v/>
       </c>
-      <c r="J435" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K435" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L435" s="6" t="n">
-        <v/>
-      </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N435" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O435" s="3" t="n">
-        <v/>
+        <v>12.26</v>
       </c>
     </row>
     <row r="436">
@@ -27865,31 +27945,33 @@
       <c r="G436" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H436" s="6" t="n">
+      <c r="H436" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I436" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J436" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K436" s="4" t="n">
         <v/>
       </c>
-      <c r="I436" s="6" t="n">
+      <c r="L436" s="4" t="n">
         <v/>
       </c>
-      <c r="J436" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K436" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L436" s="6" t="n">
-        <v/>
-      </c>
       <c r="M436" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N436" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O436" s="3" t="n">
-        <v/>
+        <v>14.62</v>
       </c>
     </row>
     <row r="437">
@@ -27926,31 +28008,33 @@
       <c r="G437" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H437" s="6" t="n">
+      <c r="H437" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K437" s="4" t="n">
         <v/>
       </c>
-      <c r="I437" s="6" t="n">
+      <c r="L437" s="4" t="n">
         <v/>
       </c>
-      <c r="J437" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K437" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L437" s="6" t="n">
-        <v/>
-      </c>
       <c r="M437" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
       <c r="N437" s="3" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="O437" s="3" t="n">
-        <v/>
+        <v>12.26</v>
       </c>
     </row>
     <row r="438">
@@ -27993,9 +28077,7 @@
       <c r="I438" s="6" t="n">
         <v/>
       </c>
-      <c r="J438" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J438" s="6" t="inlineStr"/>
       <c r="K438" s="6" t="n">
         <v/>
       </c>
@@ -28007,12 +28089,8 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N438" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O438" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N438" s="3" t="inlineStr"/>
+      <c r="O438" s="3" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -28054,9 +28132,7 @@
       <c r="I439" s="6" t="n">
         <v/>
       </c>
-      <c r="J439" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J439" s="6" t="inlineStr"/>
       <c r="K439" s="6" t="n">
         <v/>
       </c>
@@ -28068,12 +28144,8 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N439" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O439" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N439" s="3" t="inlineStr"/>
+      <c r="O439" s="3" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -28115,9 +28187,7 @@
       <c r="I440" s="6" t="n">
         <v/>
       </c>
-      <c r="J440" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J440" s="6" t="inlineStr"/>
       <c r="K440" s="6" t="n">
         <v/>
       </c>
@@ -28129,12 +28199,8 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N440" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O440" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N440" s="3" t="inlineStr"/>
+      <c r="O440" s="3" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -28176,9 +28242,7 @@
       <c r="I441" s="6" t="n">
         <v/>
       </c>
-      <c r="J441" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J441" s="6" t="inlineStr"/>
       <c r="K441" s="6" t="n">
         <v/>
       </c>
@@ -28190,12 +28254,8 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N441" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O441" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N441" s="3" t="inlineStr"/>
+      <c r="O441" s="3" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -28237,9 +28297,7 @@
       <c r="I442" s="6" t="n">
         <v/>
       </c>
-      <c r="J442" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J442" s="6" t="inlineStr"/>
       <c r="K442" s="6" t="n">
         <v/>
       </c>
@@ -28251,12 +28309,8 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N442" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O442" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N442" s="3" t="inlineStr"/>
+      <c r="O442" s="3" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -28298,9 +28352,7 @@
       <c r="I443" s="6" t="n">
         <v/>
       </c>
-      <c r="J443" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J443" s="6" t="inlineStr"/>
       <c r="K443" s="6" t="n">
         <v/>
       </c>
@@ -28312,12 +28364,8 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N443" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O443" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N443" s="3" t="inlineStr"/>
+      <c r="O443" s="3" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -28359,9 +28407,7 @@
       <c r="I444" s="6" t="n">
         <v/>
       </c>
-      <c r="J444" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J444" s="6" t="inlineStr"/>
       <c r="K444" s="6" t="n">
         <v/>
       </c>
@@ -28373,12 +28419,8 @@
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N444" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O444" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N444" s="3" t="inlineStr"/>
+      <c r="O444" s="3" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -28420,9 +28462,7 @@
       <c r="I445" s="6" t="n">
         <v/>
       </c>
-      <c r="J445" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J445" s="6" t="inlineStr"/>
       <c r="K445" s="6" t="n">
         <v/>
       </c>
@@ -28434,12 +28474,8 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N445" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O445" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N445" s="3" t="inlineStr"/>
+      <c r="O445" s="3" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -28481,9 +28517,7 @@
       <c r="I446" s="6" t="n">
         <v/>
       </c>
-      <c r="J446" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J446" s="6" t="inlineStr"/>
       <c r="K446" s="6" t="n">
         <v/>
       </c>
@@ -28495,12 +28529,8 @@
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N446" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O446" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N446" s="3" t="inlineStr"/>
+      <c r="O446" s="3" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -28542,9 +28572,7 @@
       <c r="I447" s="6" t="n">
         <v/>
       </c>
-      <c r="J447" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J447" s="6" t="inlineStr"/>
       <c r="K447" s="6" t="n">
         <v/>
       </c>
@@ -28556,12 +28584,8 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N447" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O447" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N447" s="3" t="inlineStr"/>
+      <c r="O447" s="3" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -28603,9 +28627,7 @@
       <c r="I448" s="6" t="n">
         <v/>
       </c>
-      <c r="J448" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J448" s="6" t="inlineStr"/>
       <c r="K448" s="6" t="n">
         <v/>
       </c>
@@ -28617,12 +28639,8 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N448" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O448" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N448" s="3" t="inlineStr"/>
+      <c r="O448" s="3" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -28664,9 +28682,7 @@
       <c r="I449" s="6" t="n">
         <v/>
       </c>
-      <c r="J449" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J449" s="6" t="inlineStr"/>
       <c r="K449" s="6" t="n">
         <v/>
       </c>
@@ -28678,12 +28694,8 @@
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N449" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O449" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N449" s="3" t="inlineStr"/>
+      <c r="O449" s="3" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -28725,9 +28737,7 @@
       <c r="I450" s="6" t="n">
         <v/>
       </c>
-      <c r="J450" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J450" s="6" t="inlineStr"/>
       <c r="K450" s="6" t="n">
         <v/>
       </c>
@@ -28739,12 +28749,8 @@
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N450" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O450" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N450" s="3" t="inlineStr"/>
+      <c r="O450" s="3" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -28786,9 +28792,7 @@
       <c r="I451" s="6" t="n">
         <v/>
       </c>
-      <c r="J451" s="6" t="n">
-        <v/>
-      </c>
+      <c r="J451" s="6" t="inlineStr"/>
       <c r="K451" s="6" t="n">
         <v/>
       </c>
@@ -28800,12 +28804,8 @@
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N451" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O451" s="3" t="n">
-        <v/>
-      </c>
+      <c r="N451" s="3" t="inlineStr"/>
+      <c r="O451" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Backtest_Lay_2x2_Agosto_2026.xlsx
+++ b/Backtest_Lay_2x2_Agosto_2026.xlsx
@@ -28071,26 +28071,34 @@
       <c r="G438" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H438" s="6" t="n">
+      <c r="H438" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I438" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J438" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K438" s="4" t="n">
         <v/>
       </c>
-      <c r="I438" s="6" t="n">
+      <c r="L438" s="4" t="n">
         <v/>
       </c>
-      <c r="J438" s="6" t="inlineStr"/>
-      <c r="K438" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L438" s="6" t="n">
-        <v/>
-      </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N438" s="3" t="inlineStr"/>
-      <c r="O438" s="3" t="inlineStr"/>
+      <c r="N438" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O438" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -28126,26 +28134,34 @@
       <c r="G439" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H439" s="6" t="n">
+      <c r="H439" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I439" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J439" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K439" s="4" t="n">
         <v/>
       </c>
-      <c r="I439" s="6" t="n">
+      <c r="L439" s="4" t="n">
         <v/>
       </c>
-      <c r="J439" s="6" t="inlineStr"/>
-      <c r="K439" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L439" s="6" t="n">
-        <v/>
-      </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N439" s="3" t="inlineStr"/>
-      <c r="O439" s="3" t="inlineStr"/>
+      <c r="N439" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O439" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -28181,26 +28197,34 @@
       <c r="G440" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H440" s="6" t="n">
+      <c r="H440" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I440" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J440" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K440" s="4" t="n">
         <v/>
       </c>
-      <c r="I440" s="6" t="n">
+      <c r="L440" s="4" t="n">
         <v/>
       </c>
-      <c r="J440" s="6" t="inlineStr"/>
-      <c r="K440" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L440" s="6" t="n">
-        <v/>
-      </c>
       <c r="M440" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N440" s="3" t="inlineStr"/>
-      <c r="O440" s="3" t="inlineStr"/>
+      <c r="N440" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O440" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -28236,26 +28260,34 @@
       <c r="G441" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H441" s="6" t="n">
+      <c r="H441" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I441" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J441" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K441" s="4" t="n">
         <v/>
       </c>
-      <c r="I441" s="6" t="n">
+      <c r="L441" s="4" t="n">
         <v/>
       </c>
-      <c r="J441" s="6" t="inlineStr"/>
-      <c r="K441" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L441" s="6" t="n">
-        <v/>
-      </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N441" s="3" t="inlineStr"/>
-      <c r="O441" s="3" t="inlineStr"/>
+      <c r="N441" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O441" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -28291,26 +28323,34 @@
       <c r="G442" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H442" s="6" t="n">
+      <c r="H442" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I442" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K442" s="4" t="n">
         <v/>
       </c>
-      <c r="I442" s="6" t="n">
+      <c r="L442" s="4" t="n">
         <v/>
       </c>
-      <c r="J442" s="6" t="inlineStr"/>
-      <c r="K442" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L442" s="6" t="n">
-        <v/>
-      </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N442" s="3" t="inlineStr"/>
-      <c r="O442" s="3" t="inlineStr"/>
+      <c r="N442" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O442" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -28346,26 +28386,34 @@
       <c r="G443" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H443" s="6" t="n">
+      <c r="H443" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I443" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K443" s="4" t="n">
         <v/>
       </c>
-      <c r="I443" s="6" t="n">
+      <c r="L443" s="4" t="n">
         <v/>
       </c>
-      <c r="J443" s="6" t="inlineStr"/>
-      <c r="K443" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L443" s="6" t="n">
-        <v/>
-      </c>
       <c r="M443" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N443" s="3" t="inlineStr"/>
-      <c r="O443" s="3" t="inlineStr"/>
+      <c r="N443" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O443" s="3" t="n">
+        <v>12.26</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -28401,26 +28449,34 @@
       <c r="G444" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="H444" s="6" t="n">
+      <c r="H444" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I444" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J444" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K444" s="4" t="n">
         <v/>
       </c>
-      <c r="I444" s="6" t="n">
+      <c r="L444" s="4" t="n">
         <v/>
       </c>
-      <c r="J444" s="6" t="inlineStr"/>
-      <c r="K444" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L444" s="6" t="n">
-        <v/>
-      </c>
       <c r="M444" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (13.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N444" s="3" t="inlineStr"/>
-      <c r="O444" s="3" t="inlineStr"/>
+      <c r="N444" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O444" s="3" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -28456,26 +28512,34 @@
       <c r="G445" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H445" s="6" t="n">
+      <c r="H445" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I445" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K445" s="4" t="n">
         <v/>
       </c>
-      <c r="I445" s="6" t="n">
+      <c r="L445" s="4" t="n">
         <v/>
       </c>
-      <c r="J445" s="6" t="inlineStr"/>
-      <c r="K445" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L445" s="6" t="n">
-        <v/>
-      </c>
       <c r="M445" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N445" s="3" t="inlineStr"/>
-      <c r="O445" s="3" t="inlineStr"/>
+      <c r="N445" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O445" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -28511,26 +28575,34 @@
       <c r="G446" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="H446" s="6" t="n">
+      <c r="H446" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I446" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J446" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K446" s="4" t="n">
         <v/>
       </c>
-      <c r="I446" s="6" t="n">
+      <c r="L446" s="4" t="n">
         <v/>
       </c>
-      <c r="J446" s="6" t="inlineStr"/>
-      <c r="K446" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L446" s="6" t="n">
-        <v/>
-      </c>
       <c r="M446" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (17.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N446" s="3" t="inlineStr"/>
-      <c r="O446" s="3" t="inlineStr"/>
+      <c r="N446" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O446" s="3" t="n">
+        <v>11.88</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -28566,26 +28638,34 @@
       <c r="G447" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H447" s="6" t="n">
+      <c r="H447" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I447" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J447" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K447" s="4" t="n">
         <v/>
       </c>
-      <c r="I447" s="6" t="n">
+      <c r="L447" s="4" t="n">
         <v/>
       </c>
-      <c r="J447" s="6" t="inlineStr"/>
-      <c r="K447" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L447" s="6" t="n">
-        <v/>
-      </c>
       <c r="M447" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N447" s="3" t="inlineStr"/>
-      <c r="O447" s="3" t="inlineStr"/>
+      <c r="N447" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O447" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -28621,26 +28701,34 @@
       <c r="G448" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="H448" s="6" t="n">
+      <c r="H448" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I448" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J448" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K448" s="5" t="n">
         <v/>
       </c>
-      <c r="I448" s="6" t="n">
+      <c r="L448" s="5" t="n">
         <v/>
       </c>
-      <c r="J448" s="6" t="inlineStr"/>
-      <c r="K448" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L448" s="6" t="n">
-        <v/>
-      </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (16.50) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N448" s="3" t="inlineStr"/>
-      <c r="O448" s="3" t="inlineStr"/>
+      <c r="N448" s="3" t="n">
+        <v>-1550</v>
+      </c>
+      <c r="O448" s="3" t="n">
+        <v>-200</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -28676,26 +28764,34 @@
       <c r="G449" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H449" s="6" t="n">
+      <c r="H449" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I449" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J449" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K449" s="4" t="n">
         <v/>
       </c>
-      <c r="I449" s="6" t="n">
+      <c r="L449" s="4" t="n">
         <v/>
       </c>
-      <c r="J449" s="6" t="inlineStr"/>
-      <c r="K449" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L449" s="6" t="n">
-        <v/>
-      </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (15.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N449" s="3" t="inlineStr"/>
-      <c r="O449" s="3" t="inlineStr"/>
+      <c r="N449" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O449" s="3" t="n">
+        <v>13.57</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -28731,26 +28827,34 @@
       <c r="G450" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="H450" s="6" t="n">
+      <c r="H450" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I450" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J450" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K450" s="4" t="n">
         <v/>
       </c>
-      <c r="I450" s="6" t="n">
+      <c r="L450" s="4" t="n">
         <v/>
       </c>
-      <c r="J450" s="6" t="inlineStr"/>
-      <c r="K450" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L450" s="6" t="n">
-        <v/>
-      </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
           <t>Odd Lay 2x2 (14.00) aprovada na faixa de risco 8.0 - 18.0</t>
         </is>
       </c>
-      <c r="N450" s="3" t="inlineStr"/>
-      <c r="O450" s="3" t="inlineStr"/>
+      <c r="N450" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O450" s="3" t="n">
+        <v>14.62</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
